--- a/output/version3/test/15-5/MARL/CTDE/RL-RL with CL/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-5/MARL/CTDE/RL-RL with CL/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>640</v>
+        <v>705</v>
       </c>
       <c r="C2" t="n">
-        <v>576</v>
+        <v>765</v>
       </c>
       <c r="D2" t="n">
-        <v>732</v>
+        <v>566</v>
       </c>
       <c r="E2" t="n">
-        <v>778</v>
+        <v>620</v>
       </c>
       <c r="F2" t="n">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="G2" t="n">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="H2" t="n">
-        <v>647</v>
+        <v>665</v>
       </c>
       <c r="I2" t="n">
+        <v>646</v>
+      </c>
+      <c r="J2" t="n">
+        <v>786</v>
+      </c>
+      <c r="K2" t="n">
         <v>651</v>
       </c>
-      <c r="J2" t="n">
-        <v>679</v>
-      </c>
-      <c r="K2" t="n">
-        <v>610</v>
-      </c>
       <c r="L2" t="n">
-        <v>663.6</v>
+        <v>672.6</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>779</v>
+        <v>814</v>
       </c>
       <c r="C3" t="n">
-        <v>875</v>
+        <v>787</v>
       </c>
       <c r="D3" t="n">
-        <v>830</v>
+        <v>721</v>
       </c>
       <c r="E3" t="n">
-        <v>842</v>
+        <v>719</v>
       </c>
       <c r="F3" t="n">
-        <v>756</v>
+        <v>774</v>
       </c>
       <c r="G3" t="n">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="H3" t="n">
-        <v>879</v>
+        <v>908</v>
       </c>
       <c r="I3" t="n">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="J3" t="n">
-        <v>823</v>
+        <v>788</v>
       </c>
       <c r="K3" t="n">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="L3" t="n">
-        <v>807.1</v>
+        <v>781.6</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>849</v>
+        <v>741</v>
       </c>
       <c r="C4" t="n">
-        <v>1011</v>
+        <v>731</v>
       </c>
       <c r="D4" t="n">
-        <v>841</v>
+        <v>759</v>
       </c>
       <c r="E4" t="n">
-        <v>753</v>
+        <v>769</v>
       </c>
       <c r="F4" t="n">
-        <v>797</v>
+        <v>767</v>
       </c>
       <c r="G4" t="n">
-        <v>823</v>
+        <v>695</v>
       </c>
       <c r="H4" t="n">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="I4" t="n">
-        <v>789</v>
+        <v>760</v>
       </c>
       <c r="J4" t="n">
-        <v>868</v>
+        <v>665</v>
       </c>
       <c r="K4" t="n">
-        <v>947</v>
+        <v>867</v>
       </c>
       <c r="L4" t="n">
-        <v>842.9</v>
+        <v>752</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>842</v>
+        <v>804</v>
       </c>
       <c r="C5" t="n">
-        <v>908</v>
+        <v>834</v>
       </c>
       <c r="D5" t="n">
-        <v>967</v>
+        <v>913</v>
       </c>
       <c r="E5" t="n">
-        <v>866</v>
+        <v>835</v>
       </c>
       <c r="F5" t="n">
-        <v>891</v>
+        <v>880</v>
       </c>
       <c r="G5" t="n">
-        <v>906</v>
+        <v>820</v>
       </c>
       <c r="H5" t="n">
-        <v>992</v>
+        <v>999</v>
       </c>
       <c r="I5" t="n">
-        <v>895</v>
+        <v>852</v>
       </c>
       <c r="J5" t="n">
-        <v>998</v>
+        <v>801</v>
       </c>
       <c r="K5" t="n">
-        <v>1003</v>
+        <v>913</v>
       </c>
       <c r="L5" t="n">
-        <v>926.8</v>
+        <v>865.1</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>685</v>
+        <v>717</v>
       </c>
       <c r="C6" t="n">
-        <v>680</v>
+        <v>627</v>
       </c>
       <c r="D6" t="n">
+        <v>649</v>
+      </c>
+      <c r="E6" t="n">
+        <v>712</v>
+      </c>
+      <c r="F6" t="n">
+        <v>687</v>
+      </c>
+      <c r="G6" t="n">
+        <v>681</v>
+      </c>
+      <c r="H6" t="n">
+        <v>638</v>
+      </c>
+      <c r="I6" t="n">
+        <v>714</v>
+      </c>
+      <c r="J6" t="n">
         <v>721</v>
       </c>
-      <c r="E6" t="n">
-        <v>616</v>
-      </c>
-      <c r="F6" t="n">
-        <v>692</v>
-      </c>
-      <c r="G6" t="n">
-        <v>710</v>
-      </c>
-      <c r="H6" t="n">
-        <v>641</v>
-      </c>
-      <c r="I6" t="n">
-        <v>640</v>
-      </c>
-      <c r="J6" t="n">
-        <v>612</v>
-      </c>
       <c r="K6" t="n">
-        <v>610</v>
+        <v>645</v>
       </c>
       <c r="L6" t="n">
-        <v>660.7</v>
+        <v>679.1</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>871</v>
+        <v>778</v>
       </c>
       <c r="C7" t="n">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="D7" t="n">
-        <v>901</v>
+        <v>780</v>
       </c>
       <c r="E7" t="n">
-        <v>865</v>
+        <v>981</v>
       </c>
       <c r="F7" t="n">
-        <v>801</v>
+        <v>775</v>
       </c>
       <c r="G7" t="n">
-        <v>951</v>
+        <v>850</v>
       </c>
       <c r="H7" t="n">
-        <v>990</v>
+        <v>812</v>
       </c>
       <c r="I7" t="n">
-        <v>904</v>
+        <v>818</v>
       </c>
       <c r="J7" t="n">
-        <v>920</v>
+        <v>788</v>
       </c>
       <c r="K7" t="n">
-        <v>898</v>
+        <v>760</v>
       </c>
       <c r="L7" t="n">
-        <v>899.3</v>
+        <v>823.7</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>774</v>
+        <v>708</v>
       </c>
       <c r="C8" t="n">
-        <v>829</v>
+        <v>734</v>
       </c>
       <c r="D8" t="n">
-        <v>792</v>
+        <v>751</v>
       </c>
       <c r="E8" t="n">
-        <v>834</v>
+        <v>771</v>
       </c>
       <c r="F8" t="n">
-        <v>754</v>
+        <v>669</v>
       </c>
       <c r="G8" t="n">
-        <v>715</v>
+        <v>624</v>
       </c>
       <c r="H8" t="n">
-        <v>862</v>
+        <v>691</v>
       </c>
       <c r="I8" t="n">
-        <v>710</v>
+        <v>752</v>
       </c>
       <c r="J8" t="n">
-        <v>795</v>
+        <v>819</v>
       </c>
       <c r="K8" t="n">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="L8" t="n">
-        <v>785.4</v>
+        <v>728.9</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>640</v>
+        <v>693</v>
       </c>
       <c r="C9" t="n">
-        <v>847</v>
+        <v>648</v>
       </c>
       <c r="D9" t="n">
-        <v>771</v>
+        <v>693</v>
       </c>
       <c r="E9" t="n">
-        <v>750</v>
+        <v>638</v>
       </c>
       <c r="F9" t="n">
-        <v>866</v>
+        <v>746</v>
       </c>
       <c r="G9" t="n">
-        <v>719</v>
+        <v>621</v>
       </c>
       <c r="H9" t="n">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="I9" t="n">
-        <v>660</v>
+        <v>693</v>
       </c>
       <c r="J9" t="n">
-        <v>718</v>
+        <v>673</v>
       </c>
       <c r="K9" t="n">
-        <v>699</v>
+        <v>609</v>
       </c>
       <c r="L9" t="n">
-        <v>736.1</v>
+        <v>669.1</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>947</v>
+        <v>856</v>
       </c>
       <c r="C10" t="n">
-        <v>906</v>
+        <v>883</v>
       </c>
       <c r="D10" t="n">
-        <v>862</v>
+        <v>850</v>
       </c>
       <c r="E10" t="n">
-        <v>896</v>
+        <v>753</v>
       </c>
       <c r="F10" t="n">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="G10" t="n">
-        <v>964</v>
+        <v>894</v>
       </c>
       <c r="H10" t="n">
-        <v>1071</v>
+        <v>810</v>
       </c>
       <c r="I10" t="n">
-        <v>910</v>
+        <v>796</v>
       </c>
       <c r="J10" t="n">
-        <v>873</v>
+        <v>838</v>
       </c>
       <c r="K10" t="n">
-        <v>814</v>
+        <v>836</v>
       </c>
       <c r="L10" t="n">
-        <v>913.1</v>
+        <v>840</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>798</v>
+        <v>760</v>
       </c>
       <c r="C11" t="n">
-        <v>1045</v>
+        <v>737</v>
       </c>
       <c r="D11" t="n">
-        <v>773</v>
+        <v>741</v>
       </c>
       <c r="E11" t="n">
-        <v>950</v>
+        <v>803</v>
       </c>
       <c r="F11" t="n">
-        <v>825</v>
+        <v>783</v>
       </c>
       <c r="G11" t="n">
-        <v>977</v>
+        <v>822</v>
       </c>
       <c r="H11" t="n">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="I11" t="n">
-        <v>761</v>
+        <v>887</v>
       </c>
       <c r="J11" t="n">
-        <v>962</v>
+        <v>801</v>
       </c>
       <c r="K11" t="n">
-        <v>759</v>
+        <v>890</v>
       </c>
       <c r="L11" t="n">
-        <v>863.7</v>
+        <v>800.6</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>752</v>
+        <v>663</v>
       </c>
       <c r="C12" t="n">
-        <v>748</v>
+        <v>696</v>
       </c>
       <c r="D12" t="n">
-        <v>792</v>
+        <v>714</v>
       </c>
       <c r="E12" t="n">
-        <v>764</v>
+        <v>679</v>
       </c>
       <c r="F12" t="n">
-        <v>779</v>
+        <v>696</v>
       </c>
       <c r="G12" t="n">
-        <v>786</v>
+        <v>687</v>
       </c>
       <c r="H12" t="n">
-        <v>722</v>
+        <v>698</v>
       </c>
       <c r="I12" t="n">
-        <v>781</v>
+        <v>754</v>
       </c>
       <c r="J12" t="n">
-        <v>683</v>
+        <v>721</v>
       </c>
       <c r="K12" t="n">
-        <v>830</v>
+        <v>741</v>
       </c>
       <c r="L12" t="n">
-        <v>763.7</v>
+        <v>704.9</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>713</v>
+        <v>637</v>
       </c>
       <c r="C13" t="n">
-        <v>743</v>
+        <v>662</v>
       </c>
       <c r="D13" t="n">
-        <v>769</v>
+        <v>622</v>
       </c>
       <c r="E13" t="n">
-        <v>679</v>
+        <v>658</v>
       </c>
       <c r="F13" t="n">
-        <v>683</v>
+        <v>631</v>
       </c>
       <c r="G13" t="n">
-        <v>660</v>
+        <v>645</v>
       </c>
       <c r="H13" t="n">
-        <v>739</v>
+        <v>619</v>
       </c>
       <c r="I13" t="n">
-        <v>678</v>
+        <v>691</v>
       </c>
       <c r="J13" t="n">
-        <v>670</v>
+        <v>622</v>
       </c>
       <c r="K13" t="n">
-        <v>746</v>
+        <v>612</v>
       </c>
       <c r="L13" t="n">
-        <v>708</v>
+        <v>639.9</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>669</v>
+        <v>628</v>
       </c>
       <c r="C14" t="n">
-        <v>674</v>
+        <v>629</v>
       </c>
       <c r="D14" t="n">
-        <v>721</v>
+        <v>693</v>
       </c>
       <c r="E14" t="n">
-        <v>699</v>
+        <v>615</v>
       </c>
       <c r="F14" t="n">
-        <v>723</v>
+        <v>732</v>
       </c>
       <c r="G14" t="n">
-        <v>733</v>
+        <v>652</v>
       </c>
       <c r="H14" t="n">
-        <v>693</v>
+        <v>676</v>
       </c>
       <c r="I14" t="n">
-        <v>699</v>
+        <v>598</v>
       </c>
       <c r="J14" t="n">
-        <v>661</v>
+        <v>742</v>
       </c>
       <c r="K14" t="n">
-        <v>675</v>
+        <v>633</v>
       </c>
       <c r="L14" t="n">
-        <v>694.7</v>
+        <v>659.8</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>780</v>
+        <v>759</v>
       </c>
       <c r="C15" t="n">
-        <v>844</v>
+        <v>775</v>
       </c>
       <c r="D15" t="n">
-        <v>806</v>
+        <v>927</v>
       </c>
       <c r="E15" t="n">
-        <v>958</v>
+        <v>828</v>
       </c>
       <c r="F15" t="n">
-        <v>920</v>
+        <v>762</v>
       </c>
       <c r="G15" t="n">
-        <v>825</v>
+        <v>670</v>
       </c>
       <c r="H15" t="n">
-        <v>810</v>
+        <v>767</v>
       </c>
       <c r="I15" t="n">
-        <v>876</v>
+        <v>750</v>
       </c>
       <c r="J15" t="n">
-        <v>839</v>
+        <v>753</v>
       </c>
       <c r="K15" t="n">
-        <v>672</v>
+        <v>738</v>
       </c>
       <c r="L15" t="n">
-        <v>833</v>
+        <v>772.9</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>898</v>
+        <v>859</v>
       </c>
       <c r="C16" t="n">
-        <v>909</v>
+        <v>824</v>
       </c>
       <c r="D16" t="n">
-        <v>747</v>
+        <v>734</v>
       </c>
       <c r="E16" t="n">
-        <v>832</v>
+        <v>653</v>
       </c>
       <c r="F16" t="n">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="G16" t="n">
-        <v>1041</v>
+        <v>813</v>
       </c>
       <c r="H16" t="n">
-        <v>713</v>
+        <v>733</v>
       </c>
       <c r="I16" t="n">
-        <v>768</v>
+        <v>798</v>
       </c>
       <c r="J16" t="n">
-        <v>790</v>
+        <v>677</v>
       </c>
       <c r="K16" t="n">
-        <v>811</v>
+        <v>752</v>
       </c>
       <c r="L16" t="n">
-        <v>827.5</v>
+        <v>760.1</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>853</v>
+        <v>911</v>
       </c>
       <c r="C17" t="n">
-        <v>787</v>
+        <v>799</v>
       </c>
       <c r="D17" t="n">
-        <v>804</v>
+        <v>870</v>
       </c>
       <c r="E17" t="n">
-        <v>786</v>
+        <v>841</v>
       </c>
       <c r="F17" t="n">
-        <v>796</v>
+        <v>980</v>
       </c>
       <c r="G17" t="n">
-        <v>1027</v>
+        <v>831</v>
       </c>
       <c r="H17" t="n">
-        <v>810</v>
+        <v>855</v>
       </c>
       <c r="I17" t="n">
-        <v>840</v>
+        <v>710</v>
       </c>
       <c r="J17" t="n">
-        <v>966</v>
+        <v>839</v>
       </c>
       <c r="K17" t="n">
-        <v>1028</v>
+        <v>745</v>
       </c>
       <c r="L17" t="n">
-        <v>869.7</v>
+        <v>838.1</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>751</v>
+        <v>850</v>
       </c>
       <c r="C18" t="n">
-        <v>706</v>
+        <v>746</v>
       </c>
       <c r="D18" t="n">
-        <v>714</v>
+        <v>725</v>
       </c>
       <c r="E18" t="n">
-        <v>761</v>
+        <v>650</v>
       </c>
       <c r="F18" t="n">
-        <v>826</v>
+        <v>762</v>
       </c>
       <c r="G18" t="n">
-        <v>605</v>
+        <v>673</v>
       </c>
       <c r="H18" t="n">
-        <v>785</v>
+        <v>749</v>
       </c>
       <c r="I18" t="n">
-        <v>793</v>
+        <v>740</v>
       </c>
       <c r="J18" t="n">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="K18" t="n">
-        <v>814</v>
+        <v>736</v>
       </c>
       <c r="L18" t="n">
-        <v>745.5</v>
+        <v>732.4</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>873</v>
+        <v>749</v>
       </c>
       <c r="C19" t="n">
-        <v>745</v>
+        <v>642</v>
       </c>
       <c r="D19" t="n">
-        <v>880</v>
+        <v>636</v>
       </c>
       <c r="E19" t="n">
-        <v>800</v>
+        <v>659</v>
       </c>
       <c r="F19" t="n">
-        <v>808</v>
+        <v>765</v>
       </c>
       <c r="G19" t="n">
-        <v>896</v>
+        <v>692</v>
       </c>
       <c r="H19" t="n">
-        <v>781</v>
+        <v>754</v>
       </c>
       <c r="I19" t="n">
-        <v>727</v>
+        <v>795</v>
       </c>
       <c r="J19" t="n">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="K19" t="n">
-        <v>793</v>
+        <v>780</v>
       </c>
       <c r="L19" t="n">
-        <v>805.7</v>
+        <v>723.4</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>911</v>
+        <v>642</v>
       </c>
       <c r="C20" t="n">
-        <v>690</v>
+        <v>735</v>
       </c>
       <c r="D20" t="n">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="E20" t="n">
-        <v>749</v>
+        <v>689</v>
       </c>
       <c r="F20" t="n">
-        <v>763</v>
+        <v>716</v>
       </c>
       <c r="G20" t="n">
-        <v>731</v>
+        <v>761</v>
       </c>
       <c r="H20" t="n">
-        <v>706</v>
+        <v>683</v>
       </c>
       <c r="I20" t="n">
-        <v>723</v>
+        <v>757</v>
       </c>
       <c r="J20" t="n">
-        <v>824</v>
+        <v>714</v>
       </c>
       <c r="K20" t="n">
-        <v>804</v>
+        <v>725</v>
       </c>
       <c r="L20" t="n">
-        <v>763.7</v>
+        <v>714.8</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>825</v>
+        <v>734</v>
       </c>
       <c r="C21" t="n">
-        <v>786</v>
+        <v>687</v>
       </c>
       <c r="D21" t="n">
-        <v>757</v>
+        <v>797</v>
       </c>
       <c r="E21" t="n">
-        <v>877</v>
+        <v>751</v>
       </c>
       <c r="F21" t="n">
-        <v>737</v>
+        <v>629</v>
       </c>
       <c r="G21" t="n">
-        <v>783</v>
+        <v>670</v>
       </c>
       <c r="H21" t="n">
-        <v>827</v>
+        <v>689</v>
       </c>
       <c r="I21" t="n">
-        <v>862</v>
+        <v>667</v>
       </c>
       <c r="J21" t="n">
-        <v>897</v>
+        <v>749</v>
       </c>
       <c r="K21" t="n">
-        <v>722</v>
+        <v>869</v>
       </c>
       <c r="L21" t="n">
-        <v>807.3</v>
+        <v>724.2</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>644</v>
+        <v>599</v>
       </c>
       <c r="C22" t="n">
-        <v>618</v>
+        <v>698</v>
       </c>
       <c r="D22" t="n">
-        <v>688</v>
+        <v>610</v>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>586</v>
       </c>
       <c r="F22" t="n">
-        <v>770</v>
+        <v>709</v>
       </c>
       <c r="G22" t="n">
-        <v>660</v>
+        <v>552</v>
       </c>
       <c r="H22" t="n">
-        <v>672</v>
+        <v>612</v>
       </c>
       <c r="I22" t="n">
-        <v>719</v>
+        <v>655</v>
       </c>
       <c r="J22" t="n">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="K22" t="n">
-        <v>683</v>
+        <v>567</v>
       </c>
       <c r="L22" t="n">
-        <v>677.4</v>
+        <v>625.6</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="C23" t="n">
-        <v>748</v>
+        <v>795</v>
       </c>
       <c r="D23" t="n">
-        <v>782</v>
+        <v>756</v>
       </c>
       <c r="E23" t="n">
-        <v>942</v>
+        <v>756</v>
       </c>
       <c r="F23" t="n">
-        <v>924</v>
+        <v>821</v>
       </c>
       <c r="G23" t="n">
-        <v>760</v>
+        <v>777</v>
       </c>
       <c r="H23" t="n">
-        <v>677</v>
+        <v>706</v>
       </c>
       <c r="I23" t="n">
-        <v>929</v>
+        <v>730</v>
       </c>
       <c r="J23" t="n">
-        <v>685</v>
+        <v>836</v>
       </c>
       <c r="K23" t="n">
-        <v>719</v>
+        <v>839</v>
       </c>
       <c r="L23" t="n">
-        <v>796.6</v>
+        <v>777.5</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>775</v>
+        <v>699</v>
       </c>
       <c r="C24" t="n">
-        <v>809</v>
+        <v>722</v>
       </c>
       <c r="D24" t="n">
-        <v>699</v>
+        <v>781</v>
       </c>
       <c r="E24" t="n">
-        <v>1003</v>
+        <v>795</v>
       </c>
       <c r="F24" t="n">
-        <v>771</v>
+        <v>705</v>
       </c>
       <c r="G24" t="n">
-        <v>806</v>
+        <v>618</v>
       </c>
       <c r="H24" t="n">
-        <v>769</v>
+        <v>722</v>
       </c>
       <c r="I24" t="n">
-        <v>765</v>
+        <v>704</v>
       </c>
       <c r="J24" t="n">
-        <v>747</v>
+        <v>772</v>
       </c>
       <c r="K24" t="n">
-        <v>786</v>
+        <v>675</v>
       </c>
       <c r="L24" t="n">
-        <v>793</v>
+        <v>719.3</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>779</v>
+        <v>710</v>
       </c>
       <c r="C25" t="n">
-        <v>726</v>
+        <v>671</v>
       </c>
       <c r="D25" t="n">
-        <v>767</v>
+        <v>724</v>
       </c>
       <c r="E25" t="n">
-        <v>860</v>
+        <v>815</v>
       </c>
       <c r="F25" t="n">
-        <v>762</v>
+        <v>646</v>
       </c>
       <c r="G25" t="n">
-        <v>736</v>
+        <v>688</v>
       </c>
       <c r="H25" t="n">
-        <v>775</v>
+        <v>715</v>
       </c>
       <c r="I25" t="n">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="J25" t="n">
-        <v>767</v>
+        <v>677</v>
       </c>
       <c r="K25" t="n">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="L25" t="n">
-        <v>765</v>
+        <v>717.1</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>882</v>
+        <v>789</v>
       </c>
       <c r="C26" t="n">
-        <v>817</v>
+        <v>854</v>
       </c>
       <c r="D26" t="n">
-        <v>813</v>
+        <v>768</v>
       </c>
       <c r="E26" t="n">
-        <v>913</v>
+        <v>867</v>
       </c>
       <c r="F26" t="n">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="G26" t="n">
-        <v>947</v>
+        <v>765</v>
       </c>
       <c r="H26" t="n">
-        <v>820</v>
+        <v>773</v>
       </c>
       <c r="I26" t="n">
-        <v>749</v>
+        <v>788</v>
       </c>
       <c r="J26" t="n">
-        <v>835</v>
+        <v>765</v>
       </c>
       <c r="K26" t="n">
-        <v>871</v>
+        <v>709</v>
       </c>
       <c r="L26" t="n">
-        <v>845.7</v>
+        <v>787.9</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>914</v>
+        <v>805</v>
       </c>
       <c r="C27" t="n">
-        <v>911</v>
+        <v>847</v>
       </c>
       <c r="D27" t="n">
-        <v>1130</v>
+        <v>820</v>
       </c>
       <c r="E27" t="n">
-        <v>873</v>
+        <v>807</v>
       </c>
       <c r="F27" t="n">
-        <v>1036</v>
+        <v>759</v>
       </c>
       <c r="G27" t="n">
-        <v>825</v>
+        <v>751</v>
       </c>
       <c r="H27" t="n">
-        <v>958</v>
+        <v>791</v>
       </c>
       <c r="I27" t="n">
-        <v>834</v>
+        <v>785</v>
       </c>
       <c r="J27" t="n">
-        <v>867</v>
+        <v>742</v>
       </c>
       <c r="K27" t="n">
-        <v>874</v>
+        <v>740</v>
       </c>
       <c r="L27" t="n">
-        <v>922.2</v>
+        <v>784.7</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>804</v>
+        <v>593</v>
       </c>
       <c r="C28" t="n">
-        <v>746</v>
+        <v>684</v>
       </c>
       <c r="D28" t="n">
-        <v>789</v>
+        <v>677</v>
       </c>
       <c r="E28" t="n">
-        <v>821</v>
+        <v>749</v>
       </c>
       <c r="F28" t="n">
-        <v>689</v>
+        <v>621</v>
       </c>
       <c r="G28" t="n">
-        <v>779</v>
+        <v>672</v>
       </c>
       <c r="H28" t="n">
-        <v>740</v>
+        <v>649</v>
       </c>
       <c r="I28" t="n">
-        <v>808</v>
+        <v>684</v>
       </c>
       <c r="J28" t="n">
-        <v>780</v>
+        <v>614</v>
       </c>
       <c r="K28" t="n">
-        <v>696</v>
+        <v>581</v>
       </c>
       <c r="L28" t="n">
-        <v>765.2</v>
+        <v>652.4</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>719</v>
+        <v>793</v>
       </c>
       <c r="C29" t="n">
-        <v>798</v>
+        <v>723</v>
       </c>
       <c r="D29" t="n">
+        <v>689</v>
+      </c>
+      <c r="E29" t="n">
+        <v>698</v>
+      </c>
+      <c r="F29" t="n">
+        <v>665</v>
+      </c>
+      <c r="G29" t="n">
+        <v>712</v>
+      </c>
+      <c r="H29" t="n">
+        <v>759</v>
+      </c>
+      <c r="I29" t="n">
+        <v>723</v>
+      </c>
+      <c r="J29" t="n">
+        <v>733</v>
+      </c>
+      <c r="K29" t="n">
         <v>680</v>
       </c>
-      <c r="E29" t="n">
-        <v>939</v>
-      </c>
-      <c r="F29" t="n">
-        <v>768</v>
-      </c>
-      <c r="G29" t="n">
-        <v>755</v>
-      </c>
-      <c r="H29" t="n">
-        <v>939</v>
-      </c>
-      <c r="I29" t="n">
-        <v>802</v>
-      </c>
-      <c r="J29" t="n">
-        <v>678</v>
-      </c>
-      <c r="K29" t="n">
-        <v>937</v>
-      </c>
       <c r="L29" t="n">
-        <v>801.5</v>
+        <v>717.5</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>986</v>
+        <v>724</v>
       </c>
       <c r="C30" t="n">
-        <v>865</v>
+        <v>823</v>
       </c>
       <c r="D30" t="n">
-        <v>826</v>
+        <v>714</v>
       </c>
       <c r="E30" t="n">
-        <v>831</v>
+        <v>706</v>
       </c>
       <c r="F30" t="n">
-        <v>875</v>
+        <v>703</v>
       </c>
       <c r="G30" t="n">
-        <v>738</v>
+        <v>645</v>
       </c>
       <c r="H30" t="n">
-        <v>842</v>
+        <v>758</v>
       </c>
       <c r="I30" t="n">
-        <v>917</v>
+        <v>808</v>
       </c>
       <c r="J30" t="n">
-        <v>841</v>
+        <v>803</v>
       </c>
       <c r="K30" t="n">
-        <v>878</v>
+        <v>682</v>
       </c>
       <c r="L30" t="n">
-        <v>859.9</v>
+        <v>736.6</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>745</v>
+        <v>773</v>
       </c>
       <c r="C31" t="n">
-        <v>792</v>
+        <v>723</v>
       </c>
       <c r="D31" t="n">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="E31" t="n">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="F31" t="n">
-        <v>834</v>
+        <v>702</v>
       </c>
       <c r="G31" t="n">
-        <v>755</v>
+        <v>741</v>
       </c>
       <c r="H31" t="n">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="I31" t="n">
-        <v>751</v>
+        <v>688</v>
       </c>
       <c r="J31" t="n">
-        <v>891</v>
+        <v>661</v>
       </c>
       <c r="K31" t="n">
-        <v>668</v>
+        <v>726</v>
       </c>
       <c r="L31" t="n">
-        <v>761</v>
+        <v>718.9</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>751</v>
+        <v>630</v>
       </c>
       <c r="C32" t="n">
-        <v>766</v>
+        <v>670</v>
       </c>
       <c r="D32" t="n">
-        <v>780</v>
+        <v>561</v>
       </c>
       <c r="E32" t="n">
-        <v>775</v>
+        <v>690</v>
       </c>
       <c r="F32" t="n">
-        <v>703</v>
+        <v>661</v>
       </c>
       <c r="G32" t="n">
-        <v>732</v>
+        <v>592</v>
       </c>
       <c r="H32" t="n">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="I32" t="n">
-        <v>580</v>
+        <v>721</v>
       </c>
       <c r="J32" t="n">
-        <v>716</v>
+        <v>551</v>
       </c>
       <c r="K32" t="n">
-        <v>699</v>
+        <v>800</v>
       </c>
       <c r="L32" t="n">
-        <v>719</v>
+        <v>656.5</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>818</v>
+        <v>727</v>
       </c>
       <c r="C33" t="n">
-        <v>782</v>
+        <v>795</v>
       </c>
       <c r="D33" t="n">
-        <v>744</v>
+        <v>804</v>
       </c>
       <c r="E33" t="n">
-        <v>868</v>
+        <v>773</v>
       </c>
       <c r="F33" t="n">
+        <v>709</v>
+      </c>
+      <c r="G33" t="n">
+        <v>783</v>
+      </c>
+      <c r="H33" t="n">
+        <v>746</v>
+      </c>
+      <c r="I33" t="n">
+        <v>811</v>
+      </c>
+      <c r="J33" t="n">
         <v>790</v>
       </c>
-      <c r="G33" t="n">
-        <v>786</v>
-      </c>
-      <c r="H33" t="n">
-        <v>830</v>
-      </c>
-      <c r="I33" t="n">
-        <v>758</v>
-      </c>
-      <c r="J33" t="n">
-        <v>766</v>
-      </c>
       <c r="K33" t="n">
-        <v>784</v>
+        <v>740</v>
       </c>
       <c r="L33" t="n">
-        <v>792.6</v>
+        <v>767.8</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>704</v>
+        <v>595</v>
       </c>
       <c r="C34" t="n">
+        <v>698</v>
+      </c>
+      <c r="D34" t="n">
+        <v>703</v>
+      </c>
+      <c r="E34" t="n">
+        <v>683</v>
+      </c>
+      <c r="F34" t="n">
+        <v>677</v>
+      </c>
+      <c r="G34" t="n">
+        <v>619</v>
+      </c>
+      <c r="H34" t="n">
+        <v>746</v>
+      </c>
+      <c r="I34" t="n">
+        <v>643</v>
+      </c>
+      <c r="J34" t="n">
+        <v>679</v>
+      </c>
+      <c r="K34" t="n">
         <v>678</v>
       </c>
-      <c r="D34" t="n">
-        <v>686</v>
-      </c>
-      <c r="E34" t="n">
-        <v>739</v>
-      </c>
-      <c r="F34" t="n">
-        <v>595</v>
-      </c>
-      <c r="G34" t="n">
-        <v>618</v>
-      </c>
-      <c r="H34" t="n">
-        <v>702</v>
-      </c>
-      <c r="I34" t="n">
-        <v>726</v>
-      </c>
-      <c r="J34" t="n">
-        <v>874</v>
-      </c>
-      <c r="K34" t="n">
-        <v>722</v>
-      </c>
       <c r="L34" t="n">
-        <v>704.4</v>
+        <v>672.1</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>984</v>
+        <v>735</v>
       </c>
       <c r="C35" t="n">
-        <v>939</v>
+        <v>797</v>
       </c>
       <c r="D35" t="n">
-        <v>915</v>
+        <v>760</v>
       </c>
       <c r="E35" t="n">
-        <v>789</v>
+        <v>889</v>
       </c>
       <c r="F35" t="n">
-        <v>976</v>
+        <v>846</v>
       </c>
       <c r="G35" t="n">
-        <v>856</v>
+        <v>733</v>
       </c>
       <c r="H35" t="n">
-        <v>937</v>
+        <v>741</v>
       </c>
       <c r="I35" t="n">
-        <v>842</v>
+        <v>715</v>
       </c>
       <c r="J35" t="n">
-        <v>858</v>
+        <v>805</v>
       </c>
       <c r="K35" t="n">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="L35" t="n">
-        <v>891.4</v>
+        <v>783.6</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>664</v>
+        <v>613</v>
       </c>
       <c r="C36" t="n">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D36" t="n">
-        <v>682</v>
+        <v>622</v>
       </c>
       <c r="E36" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F36" t="n">
-        <v>686</v>
+        <v>615</v>
       </c>
       <c r="G36" t="n">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="H36" t="n">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="I36" t="n">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="J36" t="n">
-        <v>633</v>
+        <v>579</v>
       </c>
       <c r="K36" t="n">
-        <v>643</v>
+        <v>628</v>
       </c>
       <c r="L36" t="n">
-        <v>648.6</v>
+        <v>620.8</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>932</v>
+        <v>643</v>
       </c>
       <c r="C37" t="n">
-        <v>872</v>
+        <v>771</v>
       </c>
       <c r="D37" t="n">
-        <v>714</v>
+        <v>794</v>
       </c>
       <c r="E37" t="n">
-        <v>804</v>
+        <v>700</v>
       </c>
       <c r="F37" t="n">
-        <v>849</v>
+        <v>750</v>
       </c>
       <c r="G37" t="n">
-        <v>876</v>
+        <v>767</v>
       </c>
       <c r="H37" t="n">
-        <v>914</v>
+        <v>705</v>
       </c>
       <c r="I37" t="n">
-        <v>802</v>
+        <v>673</v>
       </c>
       <c r="J37" t="n">
-        <v>796</v>
+        <v>767</v>
       </c>
       <c r="K37" t="n">
-        <v>875</v>
+        <v>719</v>
       </c>
       <c r="L37" t="n">
-        <v>843.4</v>
+        <v>728.9</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>769</v>
+        <v>871</v>
       </c>
       <c r="C38" t="n">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="D38" t="n">
-        <v>912</v>
+        <v>740</v>
       </c>
       <c r="E38" t="n">
-        <v>969</v>
+        <v>831</v>
       </c>
       <c r="F38" t="n">
-        <v>788</v>
+        <v>754</v>
       </c>
       <c r="G38" t="n">
-        <v>752</v>
+        <v>737</v>
       </c>
       <c r="H38" t="n">
-        <v>986</v>
+        <v>760</v>
       </c>
       <c r="I38" t="n">
-        <v>803</v>
+        <v>686</v>
       </c>
       <c r="J38" t="n">
-        <v>821</v>
+        <v>757</v>
       </c>
       <c r="K38" t="n">
-        <v>669</v>
+        <v>797</v>
       </c>
       <c r="L38" t="n">
-        <v>824.1</v>
+        <v>770.9</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>804</v>
+        <v>623</v>
       </c>
       <c r="C39" t="n">
-        <v>653</v>
+        <v>632</v>
       </c>
       <c r="D39" t="n">
-        <v>655</v>
+        <v>568</v>
       </c>
       <c r="E39" t="n">
-        <v>708</v>
+        <v>679</v>
       </c>
       <c r="F39" t="n">
-        <v>732</v>
+        <v>545</v>
       </c>
       <c r="G39" t="n">
-        <v>641</v>
+        <v>670</v>
       </c>
       <c r="H39" t="n">
-        <v>582</v>
+        <v>608</v>
       </c>
       <c r="I39" t="n">
-        <v>688</v>
+        <v>736</v>
       </c>
       <c r="J39" t="n">
-        <v>686</v>
+        <v>659</v>
       </c>
       <c r="K39" t="n">
-        <v>765</v>
+        <v>627</v>
       </c>
       <c r="L39" t="n">
-        <v>691.4</v>
+        <v>634.7</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="C40" t="n">
-        <v>788</v>
+        <v>762</v>
       </c>
       <c r="D40" t="n">
-        <v>824</v>
+        <v>759</v>
       </c>
       <c r="E40" t="n">
-        <v>803</v>
+        <v>790</v>
       </c>
       <c r="F40" t="n">
-        <v>813</v>
+        <v>719</v>
       </c>
       <c r="G40" t="n">
-        <v>764</v>
+        <v>923</v>
       </c>
       <c r="H40" t="n">
-        <v>840</v>
+        <v>818</v>
       </c>
       <c r="I40" t="n">
-        <v>890</v>
+        <v>722</v>
       </c>
       <c r="J40" t="n">
-        <v>860</v>
+        <v>837</v>
       </c>
       <c r="K40" t="n">
-        <v>779</v>
+        <v>681</v>
       </c>
       <c r="L40" t="n">
-        <v>814.4</v>
+        <v>778.9</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>773</v>
+        <v>730</v>
       </c>
       <c r="C41" t="n">
-        <v>857</v>
+        <v>732</v>
       </c>
       <c r="D41" t="n">
+        <v>657</v>
+      </c>
+      <c r="E41" t="n">
+        <v>717</v>
+      </c>
+      <c r="F41" t="n">
+        <v>689</v>
+      </c>
+      <c r="G41" t="n">
+        <v>722</v>
+      </c>
+      <c r="H41" t="n">
         <v>669</v>
       </c>
-      <c r="E41" t="n">
-        <v>849</v>
-      </c>
-      <c r="F41" t="n">
-        <v>709</v>
-      </c>
-      <c r="G41" t="n">
-        <v>725</v>
-      </c>
-      <c r="H41" t="n">
-        <v>824</v>
-      </c>
       <c r="I41" t="n">
-        <v>857</v>
+        <v>679</v>
       </c>
       <c r="J41" t="n">
-        <v>856</v>
+        <v>679</v>
       </c>
       <c r="K41" t="n">
-        <v>817</v>
+        <v>702</v>
       </c>
       <c r="L41" t="n">
-        <v>793.6</v>
+        <v>697.6</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>716</v>
+        <v>650</v>
       </c>
       <c r="C42" t="n">
-        <v>718</v>
+        <v>576</v>
       </c>
       <c r="D42" t="n">
-        <v>739</v>
+        <v>713</v>
       </c>
       <c r="E42" t="n">
-        <v>674</v>
+        <v>624</v>
       </c>
       <c r="F42" t="n">
-        <v>672</v>
+        <v>624</v>
       </c>
       <c r="G42" t="n">
-        <v>617</v>
+        <v>641</v>
       </c>
       <c r="H42" t="n">
-        <v>570</v>
+        <v>630</v>
       </c>
       <c r="I42" t="n">
-        <v>629</v>
+        <v>761</v>
       </c>
       <c r="J42" t="n">
-        <v>733</v>
+        <v>595</v>
       </c>
       <c r="K42" t="n">
-        <v>654</v>
+        <v>690</v>
       </c>
       <c r="L42" t="n">
-        <v>672.2</v>
+        <v>650.4</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>723</v>
+        <v>762</v>
       </c>
       <c r="C43" t="n">
-        <v>844</v>
+        <v>810</v>
       </c>
       <c r="D43" t="n">
-        <v>721</v>
+        <v>795</v>
       </c>
       <c r="E43" t="n">
+        <v>900</v>
+      </c>
+      <c r="F43" t="n">
+        <v>811</v>
+      </c>
+      <c r="G43" t="n">
         <v>816</v>
       </c>
-      <c r="F43" t="n">
-        <v>763</v>
-      </c>
-      <c r="G43" t="n">
-        <v>855</v>
-      </c>
       <c r="H43" t="n">
-        <v>801</v>
+        <v>851</v>
       </c>
       <c r="I43" t="n">
-        <v>759</v>
+        <v>831</v>
       </c>
       <c r="J43" t="n">
-        <v>831</v>
+        <v>770</v>
       </c>
       <c r="K43" t="n">
-        <v>908</v>
+        <v>875</v>
       </c>
       <c r="L43" t="n">
-        <v>802.1</v>
+        <v>822.1</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>851</v>
+        <v>740</v>
       </c>
       <c r="C44" t="n">
+        <v>778</v>
+      </c>
+      <c r="D44" t="n">
         <v>752</v>
       </c>
-      <c r="D44" t="n">
-        <v>775</v>
-      </c>
       <c r="E44" t="n">
-        <v>785</v>
+        <v>824</v>
       </c>
       <c r="F44" t="n">
-        <v>772</v>
+        <v>733</v>
       </c>
       <c r="G44" t="n">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="H44" t="n">
-        <v>803</v>
+        <v>745</v>
       </c>
       <c r="I44" t="n">
-        <v>733</v>
+        <v>794</v>
       </c>
       <c r="J44" t="n">
-        <v>707</v>
+        <v>855</v>
       </c>
       <c r="K44" t="n">
-        <v>936</v>
+        <v>766</v>
       </c>
       <c r="L44" t="n">
-        <v>786.7</v>
+        <v>773.3</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>773</v>
+        <v>585</v>
       </c>
       <c r="C45" t="n">
-        <v>681</v>
+        <v>648</v>
       </c>
       <c r="D45" t="n">
-        <v>729</v>
+        <v>647</v>
       </c>
       <c r="E45" t="n">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="F45" t="n">
-        <v>749</v>
+        <v>637</v>
       </c>
       <c r="G45" t="n">
-        <v>702</v>
+        <v>654</v>
       </c>
       <c r="H45" t="n">
-        <v>663</v>
+        <v>578</v>
       </c>
       <c r="I45" t="n">
-        <v>720</v>
+        <v>661</v>
       </c>
       <c r="J45" t="n">
-        <v>721</v>
+        <v>644</v>
       </c>
       <c r="K45" t="n">
-        <v>790</v>
+        <v>580</v>
       </c>
       <c r="L45" t="n">
-        <v>721.9</v>
+        <v>631.9</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
+        <v>591</v>
+      </c>
+      <c r="C46" t="n">
+        <v>691</v>
+      </c>
+      <c r="D46" t="n">
+        <v>630</v>
+      </c>
+      <c r="E46" t="n">
+        <v>668</v>
+      </c>
+      <c r="F46" t="n">
+        <v>621</v>
+      </c>
+      <c r="G46" t="n">
+        <v>696</v>
+      </c>
+      <c r="H46" t="n">
         <v>711</v>
       </c>
-      <c r="C46" t="n">
-        <v>730</v>
-      </c>
-      <c r="D46" t="n">
-        <v>856</v>
-      </c>
-      <c r="E46" t="n">
-        <v>743</v>
-      </c>
-      <c r="F46" t="n">
-        <v>630</v>
-      </c>
-      <c r="G46" t="n">
-        <v>734</v>
-      </c>
-      <c r="H46" t="n">
-        <v>696</v>
-      </c>
       <c r="I46" t="n">
-        <v>670</v>
+        <v>731</v>
       </c>
       <c r="J46" t="n">
-        <v>859</v>
+        <v>644</v>
       </c>
       <c r="K46" t="n">
-        <v>819</v>
+        <v>664</v>
       </c>
       <c r="L46" t="n">
-        <v>744.8</v>
+        <v>664.7</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>878</v>
+        <v>747</v>
       </c>
       <c r="C47" t="n">
-        <v>888</v>
+        <v>703</v>
       </c>
       <c r="D47" t="n">
-        <v>858</v>
+        <v>841</v>
       </c>
       <c r="E47" t="n">
-        <v>902</v>
+        <v>785</v>
       </c>
       <c r="F47" t="n">
-        <v>884</v>
+        <v>816</v>
       </c>
       <c r="G47" t="n">
-        <v>1031</v>
+        <v>739</v>
       </c>
       <c r="H47" t="n">
-        <v>928</v>
+        <v>919</v>
       </c>
       <c r="I47" t="n">
-        <v>794</v>
+        <v>721</v>
       </c>
       <c r="J47" t="n">
-        <v>920</v>
+        <v>897</v>
       </c>
       <c r="K47" t="n">
-        <v>799</v>
+        <v>899</v>
       </c>
       <c r="L47" t="n">
-        <v>888.2</v>
+        <v>806.7</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>714</v>
+        <v>612</v>
       </c>
       <c r="C48" t="n">
-        <v>986</v>
+        <v>652</v>
       </c>
       <c r="D48" t="n">
-        <v>832</v>
+        <v>691</v>
       </c>
       <c r="E48" t="n">
-        <v>859</v>
+        <v>697</v>
       </c>
       <c r="F48" t="n">
-        <v>740</v>
+        <v>749</v>
       </c>
       <c r="G48" t="n">
-        <v>732</v>
+        <v>689</v>
       </c>
       <c r="H48" t="n">
-        <v>874</v>
+        <v>633</v>
       </c>
       <c r="I48" t="n">
-        <v>700</v>
+        <v>607</v>
       </c>
       <c r="J48" t="n">
-        <v>860</v>
+        <v>650</v>
       </c>
       <c r="K48" t="n">
-        <v>726</v>
+        <v>650</v>
       </c>
       <c r="L48" t="n">
-        <v>802.3</v>
+        <v>663</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>928</v>
+        <v>818</v>
       </c>
       <c r="C49" t="n">
-        <v>910</v>
+        <v>776</v>
       </c>
       <c r="D49" t="n">
-        <v>957</v>
+        <v>732</v>
       </c>
       <c r="E49" t="n">
-        <v>808</v>
+        <v>832</v>
       </c>
       <c r="F49" t="n">
-        <v>810</v>
+        <v>831</v>
       </c>
       <c r="G49" t="n">
-        <v>938</v>
+        <v>876</v>
       </c>
       <c r="H49" t="n">
-        <v>983</v>
+        <v>854</v>
       </c>
       <c r="I49" t="n">
-        <v>816</v>
+        <v>914</v>
       </c>
       <c r="J49" t="n">
-        <v>881</v>
+        <v>912</v>
       </c>
       <c r="K49" t="n">
-        <v>784</v>
+        <v>802</v>
       </c>
       <c r="L49" t="n">
-        <v>881.5</v>
+        <v>834.7</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>734</v>
+        <v>668</v>
       </c>
       <c r="C50" t="n">
-        <v>710</v>
+        <v>652</v>
       </c>
       <c r="D50" t="n">
-        <v>724</v>
+        <v>655</v>
       </c>
       <c r="E50" t="n">
-        <v>704</v>
+        <v>653</v>
       </c>
       <c r="F50" t="n">
-        <v>698</v>
+        <v>646</v>
       </c>
       <c r="G50" t="n">
+        <v>639</v>
+      </c>
+      <c r="H50" t="n">
         <v>648</v>
       </c>
-      <c r="H50" t="n">
-        <v>702</v>
-      </c>
       <c r="I50" t="n">
-        <v>739</v>
+        <v>638</v>
       </c>
       <c r="J50" t="n">
-        <v>623</v>
+        <v>582</v>
       </c>
       <c r="K50" t="n">
-        <v>740</v>
+        <v>558</v>
       </c>
       <c r="L50" t="n">
-        <v>702.2</v>
+        <v>633.9</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>776</v>
+        <v>906</v>
       </c>
       <c r="C51" t="n">
-        <v>846</v>
+        <v>687</v>
       </c>
       <c r="D51" t="n">
-        <v>751</v>
+        <v>695</v>
       </c>
       <c r="E51" t="n">
-        <v>730</v>
+        <v>704</v>
       </c>
       <c r="F51" t="n">
-        <v>707</v>
+        <v>720</v>
       </c>
       <c r="G51" t="n">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="H51" t="n">
-        <v>899</v>
+        <v>677</v>
       </c>
       <c r="I51" t="n">
-        <v>807</v>
+        <v>702</v>
       </c>
       <c r="J51" t="n">
-        <v>817</v>
+        <v>724</v>
       </c>
       <c r="K51" t="n">
-        <v>726</v>
+        <v>660</v>
       </c>
       <c r="L51" t="n">
-        <v>777.8</v>
+        <v>718.7</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>793.6799999999999</v>
+        <v>725.52</v>
       </c>
       <c r="C52" t="n">
-        <v>797.7</v>
+        <v>733.24</v>
       </c>
       <c r="D52" t="n">
-        <v>787.02</v>
+        <v>725.42</v>
       </c>
       <c r="E52" t="n">
-        <v>804.9</v>
+        <v>737.02</v>
       </c>
       <c r="F52" t="n">
-        <v>781.5</v>
+        <v>727.24</v>
       </c>
       <c r="G52" t="n">
-        <v>780.88</v>
+        <v>714.64</v>
       </c>
       <c r="H52" t="n">
-        <v>793.62</v>
+        <v>730.9400000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>769.72</v>
+        <v>734.86</v>
       </c>
       <c r="J52" t="n">
-        <v>792.0599999999999</v>
+        <v>731.98</v>
       </c>
       <c r="K52" t="n">
-        <v>780.4400000000001</v>
+        <v>725.52</v>
       </c>
       <c r="L52" t="n">
-        <v>788.1520000000002</v>
+        <v>728.638</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4.457334756851196</v>
+        <v>4.463065147399902</v>
       </c>
       <c r="C2" t="n">
-        <v>4.172407150268555</v>
+        <v>4.458077669143677</v>
       </c>
       <c r="D2" t="n">
-        <v>4.608668327331543</v>
+        <v>3.749971389770508</v>
       </c>
       <c r="E2" t="n">
-        <v>4.592594146728516</v>
+        <v>4.253625154495239</v>
       </c>
       <c r="F2" t="n">
-        <v>4.39790678024292</v>
+        <v>4.304489612579346</v>
       </c>
       <c r="G2" t="n">
-        <v>4.26595401763916</v>
+        <v>4.230686187744141</v>
       </c>
       <c r="H2" t="n">
-        <v>4.466765880584717</v>
+        <v>4.40222692489624</v>
       </c>
       <c r="I2" t="n">
-        <v>4.336324453353882</v>
+        <v>4.262601375579834</v>
       </c>
       <c r="J2" t="n">
-        <v>4.164185762405396</v>
+        <v>4.580749750137329</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2441565990448</v>
+        <v>4.32244086265564</v>
       </c>
       <c r="L2" t="n">
-        <v>4.370629787445068</v>
+        <v>4.302793407440186</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>4.578939914703369</v>
+        <v>5.122301816940308</v>
       </c>
       <c r="C3" t="n">
-        <v>4.899844884872437</v>
+        <v>4.330419778823853</v>
       </c>
       <c r="D3" t="n">
-        <v>4.58853006362915</v>
+        <v>4.660536766052246</v>
       </c>
       <c r="E3" t="n">
-        <v>4.856008291244507</v>
+        <v>4.412201642990112</v>
       </c>
       <c r="F3" t="n">
-        <v>4.614131689071655</v>
+        <v>5.336728096008301</v>
       </c>
       <c r="G3" t="n">
-        <v>4.857765913009644</v>
+        <v>4.638595819473267</v>
       </c>
       <c r="H3" t="n">
-        <v>4.697301864624023</v>
+        <v>4.341389894485474</v>
       </c>
       <c r="I3" t="n">
-        <v>4.461158990859985</v>
+        <v>4.667518615722656</v>
       </c>
       <c r="J3" t="n">
-        <v>4.44489049911499</v>
+        <v>4.996637582778931</v>
       </c>
       <c r="K3" t="n">
-        <v>4.41492223739624</v>
+        <v>4.548835754394531</v>
       </c>
       <c r="L3" t="n">
-        <v>4.6413494348526</v>
+        <v>4.705516576766968</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>5.100154399871826</v>
+        <v>4.655858278274536</v>
       </c>
       <c r="C4" t="n">
-        <v>5.683973550796509</v>
+        <v>5.378616571426392</v>
       </c>
       <c r="D4" t="n">
-        <v>5.126867771148682</v>
+        <v>4.72636079788208</v>
       </c>
       <c r="E4" t="n">
-        <v>4.873751640319824</v>
+        <v>5.653948545455933</v>
       </c>
       <c r="F4" t="n">
-        <v>4.993559837341309</v>
+        <v>4.89889931678772</v>
       </c>
       <c r="G4" t="n">
-        <v>5.491588830947876</v>
+        <v>4.684473276138306</v>
       </c>
       <c r="H4" t="n">
-        <v>5.022441148757935</v>
+        <v>4.673502683639526</v>
       </c>
       <c r="I4" t="n">
-        <v>4.768201112747192</v>
+        <v>4.666520595550537</v>
       </c>
       <c r="J4" t="n">
-        <v>5.205947160720825</v>
+        <v>4.31745457649231</v>
       </c>
       <c r="K4" t="n">
-        <v>5.486317157745361</v>
+        <v>5.012594223022461</v>
       </c>
       <c r="L4" t="n">
-        <v>5.175280261039734</v>
+        <v>4.86682288646698</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>4.976883172988892</v>
+        <v>4.797171592712402</v>
       </c>
       <c r="C5" t="n">
-        <v>5.128675222396851</v>
+        <v>4.716387748718262</v>
       </c>
       <c r="D5" t="n">
-        <v>5.169539451599121</v>
+        <v>5.309799909591675</v>
       </c>
       <c r="E5" t="n">
-        <v>4.907299757003784</v>
+        <v>5.074430227279663</v>
       </c>
       <c r="F5" t="n">
-        <v>4.862161159515381</v>
+        <v>5.05449652671814</v>
       </c>
       <c r="G5" t="n">
-        <v>5.211658716201782</v>
+        <v>4.964723348617554</v>
       </c>
       <c r="H5" t="n">
-        <v>5.167314529418945</v>
+        <v>5.392579317092896</v>
       </c>
       <c r="I5" t="n">
-        <v>5.068517684936523</v>
+        <v>4.764259815216064</v>
       </c>
       <c r="J5" t="n">
-        <v>5.031001091003418</v>
+        <v>4.988658905029297</v>
       </c>
       <c r="K5" t="n">
-        <v>5.307527303695679</v>
+        <v>5.394573926925659</v>
       </c>
       <c r="L5" t="n">
-        <v>5.083057808876037</v>
+        <v>5.045708131790161</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>3.982022523880005</v>
+        <v>3.813801050186157</v>
       </c>
       <c r="C6" t="n">
-        <v>4.044616222381592</v>
+        <v>3.411876440048218</v>
       </c>
       <c r="D6" t="n">
-        <v>3.980634450912476</v>
+        <v>3.59039831161499</v>
       </c>
       <c r="E6" t="n">
-        <v>4.008904457092285</v>
+        <v>3.795849084854126</v>
       </c>
       <c r="F6" t="n">
-        <v>4.125450611114502</v>
+        <v>3.489668369293213</v>
       </c>
       <c r="G6" t="n">
-        <v>4.211994409561157</v>
+        <v>4.149909973144531</v>
       </c>
       <c r="H6" t="n">
-        <v>3.951337099075317</v>
+        <v>3.478696823120117</v>
       </c>
       <c r="I6" t="n">
-        <v>3.847769260406494</v>
+        <v>3.601369619369507</v>
       </c>
       <c r="J6" t="n">
-        <v>3.934091806411743</v>
+        <v>3.88662314414978</v>
       </c>
       <c r="K6" t="n">
-        <v>3.874709129333496</v>
+        <v>3.527953147888184</v>
       </c>
       <c r="L6" t="n">
-        <v>3.996152997016907</v>
+        <v>3.674614596366882</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>5.281485557556152</v>
+        <v>4.650894641876221</v>
       </c>
       <c r="C7" t="n">
-        <v>5.014528274536133</v>
+        <v>4.749939441680908</v>
       </c>
       <c r="D7" t="n">
-        <v>4.918622255325317</v>
+        <v>4.437180995941162</v>
       </c>
       <c r="E7" t="n">
-        <v>4.931911945343018</v>
+        <v>5.488222360610962</v>
       </c>
       <c r="F7" t="n">
-        <v>4.906274318695068</v>
+        <v>4.696224689483643</v>
       </c>
       <c r="G7" t="n">
-        <v>4.882096767425537</v>
+        <v>4.880526781082153</v>
       </c>
       <c r="H7" t="n">
-        <v>5.35271692276001</v>
+        <v>4.683502674102783</v>
       </c>
       <c r="I7" t="n">
-        <v>5.433376312255859</v>
+        <v>4.297512054443359</v>
       </c>
       <c r="J7" t="n">
-        <v>4.917031526565552</v>
+        <v>4.346450567245483</v>
       </c>
       <c r="K7" t="n">
-        <v>5.035620927810669</v>
+        <v>4.839181184768677</v>
       </c>
       <c r="L7" t="n">
-        <v>5.067366480827332</v>
+        <v>4.706963539123535</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>4.482752561569214</v>
+        <v>3.734158992767334</v>
       </c>
       <c r="C8" t="n">
-        <v>4.296535968780518</v>
+        <v>3.893235206604004</v>
       </c>
       <c r="D8" t="n">
-        <v>4.169991731643677</v>
+        <v>4.090713739395142</v>
       </c>
       <c r="E8" t="n">
-        <v>4.590763092041016</v>
+        <v>4.089974880218506</v>
       </c>
       <c r="F8" t="n">
-        <v>4.158709526062012</v>
+        <v>3.919525623321533</v>
       </c>
       <c r="G8" t="n">
-        <v>3.999974727630615</v>
+        <v>3.862372636795044</v>
       </c>
       <c r="H8" t="n">
-        <v>4.256341457366943</v>
+        <v>3.97480845451355</v>
       </c>
       <c r="I8" t="n">
-        <v>4.125248908996582</v>
+        <v>4.110792398452759</v>
       </c>
       <c r="J8" t="n">
-        <v>4.211248397827148</v>
+        <v>3.948747158050537</v>
       </c>
       <c r="K8" t="n">
-        <v>4.205679655075073</v>
+        <v>3.957048177719116</v>
       </c>
       <c r="L8" t="n">
-        <v>4.249724602699279</v>
+        <v>3.958137726783753</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>4.186286211013794</v>
+        <v>3.730575084686279</v>
       </c>
       <c r="C9" t="n">
-        <v>4.502066850662231</v>
+        <v>3.574640512466431</v>
       </c>
       <c r="D9" t="n">
-        <v>4.154070138931274</v>
+        <v>3.616626977920532</v>
       </c>
       <c r="E9" t="n">
-        <v>3.951432228088379</v>
+        <v>3.918175220489502</v>
       </c>
       <c r="F9" t="n">
-        <v>4.489043474197388</v>
+        <v>3.771758556365967</v>
       </c>
       <c r="G9" t="n">
-        <v>3.837208032608032</v>
+        <v>3.69285249710083</v>
       </c>
       <c r="H9" t="n">
-        <v>3.730551958084106</v>
+        <v>3.94643497467041</v>
       </c>
       <c r="I9" t="n">
-        <v>4.032360553741455</v>
+        <v>4.049102067947388</v>
       </c>
       <c r="J9" t="n">
-        <v>4.334717273712158</v>
+        <v>4.169666528701782</v>
       </c>
       <c r="K9" t="n">
-        <v>3.939087390899658</v>
+        <v>3.555737018585205</v>
       </c>
       <c r="L9" t="n">
-        <v>4.115682411193847</v>
+        <v>3.802556943893433</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>5.10249400138855</v>
+        <v>4.913084506988525</v>
       </c>
       <c r="C10" t="n">
-        <v>4.908495903015137</v>
+        <v>5.027351140975952</v>
       </c>
       <c r="D10" t="n">
-        <v>4.888549566268921</v>
+        <v>4.859176635742188</v>
       </c>
       <c r="E10" t="n">
-        <v>5.185442686080933</v>
+        <v>4.721581220626831</v>
       </c>
       <c r="F10" t="n">
-        <v>5.726409435272217</v>
+        <v>4.479586362838745</v>
       </c>
       <c r="G10" t="n">
-        <v>5.795892477035522</v>
+        <v>5.536665439605713</v>
       </c>
       <c r="H10" t="n">
-        <v>5.559501886367798</v>
+        <v>4.778460264205933</v>
       </c>
       <c r="I10" t="n">
-        <v>5.29932713508606</v>
+        <v>5.221819400787354</v>
       </c>
       <c r="J10" t="n">
-        <v>5.317365646362305</v>
+        <v>4.812720775604248</v>
       </c>
       <c r="K10" t="n">
-        <v>5.207188129425049</v>
+        <v>4.902077674865723</v>
       </c>
       <c r="L10" t="n">
-        <v>5.299066686630249</v>
+        <v>4.925252342224121</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.681910991668701</v>
+        <v>4.37465500831604</v>
       </c>
       <c r="C11" t="n">
-        <v>5.738097429275513</v>
+        <v>4.372965097427368</v>
       </c>
       <c r="D11" t="n">
-        <v>4.576508045196533</v>
+        <v>4.37603759765625</v>
       </c>
       <c r="E11" t="n">
-        <v>4.914437532424927</v>
+        <v>4.565373182296753</v>
       </c>
       <c r="F11" t="n">
-        <v>4.920620679855347</v>
+        <v>4.729749202728271</v>
       </c>
       <c r="G11" t="n">
-        <v>6.01413893699646</v>
+        <v>4.880944490432739</v>
       </c>
       <c r="H11" t="n">
-        <v>5.028432130813599</v>
+        <v>5.26019287109375</v>
       </c>
       <c r="I11" t="n">
-        <v>4.471209526062012</v>
+        <v>5.446059703826904</v>
       </c>
       <c r="J11" t="n">
-        <v>5.13139820098877</v>
+        <v>4.745553016662598</v>
       </c>
       <c r="K11" t="n">
-        <v>4.709295034408569</v>
+        <v>5.601185083389282</v>
       </c>
       <c r="L11" t="n">
-        <v>5.018604850769043</v>
+        <v>4.835271525382995</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>3.969840526580811</v>
+        <v>4.4590744972229</v>
       </c>
       <c r="C12" t="n">
-        <v>4.011125087738037</v>
+        <v>4.39225435256958</v>
       </c>
       <c r="D12" t="n">
-        <v>4.101651191711426</v>
+        <v>3.987336874008179</v>
       </c>
       <c r="E12" t="n">
-        <v>4.048287391662598</v>
+        <v>3.766582727432251</v>
       </c>
       <c r="F12" t="n">
-        <v>3.969693660736084</v>
+        <v>3.964399099349976</v>
       </c>
       <c r="G12" t="n">
-        <v>4.039868831634521</v>
+        <v>4.20902681350708</v>
       </c>
       <c r="H12" t="n">
-        <v>3.906448841094971</v>
+        <v>3.70124077796936</v>
       </c>
       <c r="I12" t="n">
-        <v>4.150367021560669</v>
+        <v>4.079092025756836</v>
       </c>
       <c r="J12" t="n">
-        <v>4.066043138504028</v>
+        <v>4.617651462554932</v>
       </c>
       <c r="K12" t="n">
-        <v>4.76003623008728</v>
+        <v>4.983672618865967</v>
       </c>
       <c r="L12" t="n">
-        <v>4.102336192131043</v>
+        <v>4.216033124923706</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>4.142773151397705</v>
+        <v>4.532877922058105</v>
       </c>
       <c r="C13" t="n">
-        <v>4.648021459579468</v>
+        <v>4.361337184906006</v>
       </c>
       <c r="D13" t="n">
-        <v>4.621692657470703</v>
+        <v>4.445112705230713</v>
       </c>
       <c r="E13" t="n">
-        <v>4.106547832489014</v>
+        <v>4.606681108474731</v>
       </c>
       <c r="F13" t="n">
-        <v>4.182224035263062</v>
+        <v>4.397240877151489</v>
       </c>
       <c r="G13" t="n">
-        <v>4.053737640380859</v>
+        <v>4.04019570350647</v>
       </c>
       <c r="H13" t="n">
-        <v>4.570844888687134</v>
+        <v>4.014264106750488</v>
       </c>
       <c r="I13" t="n">
-        <v>4.372590065002441</v>
+        <v>4.470805406570435</v>
       </c>
       <c r="J13" t="n">
-        <v>4.015375137329102</v>
+        <v>4.113998174667358</v>
       </c>
       <c r="K13" t="n">
-        <v>4.399986267089844</v>
+        <v>3.981353282928467</v>
       </c>
       <c r="L13" t="n">
-        <v>4.311379313468933</v>
+        <v>4.296386647224426</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>4.328643083572388</v>
+        <v>4.019251585006714</v>
       </c>
       <c r="C14" t="n">
-        <v>4.406532526016235</v>
+        <v>4.197557926177979</v>
       </c>
       <c r="D14" t="n">
-        <v>4.053190231323242</v>
+        <v>4.528888702392578</v>
       </c>
       <c r="E14" t="n">
-        <v>4.482480049133301</v>
+        <v>3.920515537261963</v>
       </c>
       <c r="F14" t="n">
-        <v>4.415861845016479</v>
+        <v>4.376296758651733</v>
       </c>
       <c r="G14" t="n">
-        <v>4.278898239135742</v>
+        <v>3.927496910095215</v>
       </c>
       <c r="H14" t="n">
-        <v>4.270641326904297</v>
+        <v>4.221502065658569</v>
       </c>
       <c r="I14" t="n">
-        <v>4.259760141372681</v>
+        <v>4.225698947906494</v>
       </c>
       <c r="J14" t="n">
-        <v>4.172712564468384</v>
+        <v>4.911864757537842</v>
       </c>
       <c r="K14" t="n">
-        <v>4.427273273468018</v>
+        <v>4.10560941696167</v>
       </c>
       <c r="L14" t="n">
-        <v>4.309599328041076</v>
+        <v>4.243468260765075</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>4.740362167358398</v>
+        <v>4.203757286071777</v>
       </c>
       <c r="C15" t="n">
-        <v>4.812953472137451</v>
+        <v>4.523021697998047</v>
       </c>
       <c r="D15" t="n">
-        <v>4.794930458068848</v>
+        <v>5.325758218765259</v>
       </c>
       <c r="E15" t="n">
-        <v>5.143153429031372</v>
+        <v>4.514925718307495</v>
       </c>
       <c r="F15" t="n">
-        <v>4.941450834274292</v>
+        <v>4.454089164733887</v>
       </c>
       <c r="G15" t="n">
-        <v>4.652778387069702</v>
+        <v>4.082084178924561</v>
       </c>
       <c r="H15" t="n">
-        <v>4.954478979110718</v>
+        <v>4.67350172996521</v>
       </c>
       <c r="I15" t="n">
-        <v>4.889445304870605</v>
+        <v>4.508941650390625</v>
       </c>
       <c r="J15" t="n">
-        <v>4.803039789199829</v>
+        <v>4.218718767166138</v>
       </c>
       <c r="K15" t="n">
-        <v>4.539986371994019</v>
+        <v>4.371309757232666</v>
       </c>
       <c r="L15" t="n">
-        <v>4.827257919311523</v>
+        <v>4.487610816955566</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>4.757038116455078</v>
+        <v>5.072435140609741</v>
       </c>
       <c r="C16" t="n">
-        <v>4.388562917709351</v>
+        <v>4.479022026062012</v>
       </c>
       <c r="D16" t="n">
-        <v>4.313010692596436</v>
+        <v>4.302493810653687</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4929518699646</v>
+        <v>4.147908926010132</v>
       </c>
       <c r="F16" t="n">
-        <v>4.247076511383057</v>
+        <v>4.446110010147095</v>
       </c>
       <c r="G16" t="n">
-        <v>5.38184928894043</v>
+        <v>4.865585565567017</v>
       </c>
       <c r="H16" t="n">
-        <v>4.426606893539429</v>
+        <v>4.666521310806274</v>
       </c>
       <c r="I16" t="n">
-        <v>4.134904146194458</v>
+        <v>4.388265609741211</v>
       </c>
       <c r="J16" t="n">
-        <v>4.363068342208862</v>
+        <v>4.234675645828247</v>
       </c>
       <c r="K16" t="n">
-        <v>4.962372064590454</v>
+        <v>4.620787858963013</v>
       </c>
       <c r="L16" t="n">
-        <v>4.546744084358215</v>
+        <v>4.522380590438843</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.54274582862854</v>
+        <v>5.181143999099731</v>
       </c>
       <c r="C17" t="n">
-        <v>4.797842979431152</v>
+        <v>4.66253137588501</v>
       </c>
       <c r="D17" t="n">
-        <v>4.260681629180908</v>
+        <v>4.837064743041992</v>
       </c>
       <c r="E17" t="n">
-        <v>4.674220561981201</v>
+        <v>4.326430320739746</v>
       </c>
       <c r="F17" t="n">
-        <v>4.568773984909058</v>
+        <v>5.489447832107544</v>
       </c>
       <c r="G17" t="n">
-        <v>5.030085563659668</v>
+        <v>4.641587018966675</v>
       </c>
       <c r="H17" t="n">
-        <v>4.652311086654663</v>
+        <v>4.608676195144653</v>
       </c>
       <c r="I17" t="n">
-        <v>4.549385786056519</v>
+        <v>4.202760934829712</v>
       </c>
       <c r="J17" t="n">
-        <v>4.664500951766968</v>
+        <v>4.781763792037964</v>
       </c>
       <c r="K17" t="n">
-        <v>5.397531747817993</v>
+        <v>4.701322317123413</v>
       </c>
       <c r="L17" t="n">
-        <v>4.713808012008667</v>
+        <v>4.743272852897644</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>4.096577882766724</v>
+        <v>4.150899171829224</v>
       </c>
       <c r="C18" t="n">
-        <v>4.034491062164307</v>
+        <v>4.250632524490356</v>
       </c>
       <c r="D18" t="n">
-        <v>4.137146949768066</v>
+        <v>3.879976272583008</v>
       </c>
       <c r="E18" t="n">
-        <v>4.069550275802612</v>
+        <v>3.703096628189087</v>
       </c>
       <c r="F18" t="n">
-        <v>4.218116283416748</v>
+        <v>4.231683731079102</v>
       </c>
       <c r="G18" t="n">
-        <v>4.09369969367981</v>
+        <v>3.740996599197388</v>
       </c>
       <c r="H18" t="n">
-        <v>4.09190845489502</v>
+        <v>4.067529201507568</v>
       </c>
       <c r="I18" t="n">
-        <v>3.806014537811279</v>
+        <v>3.886606693267822</v>
       </c>
       <c r="J18" t="n">
-        <v>4.016676664352417</v>
+        <v>4.024237871170044</v>
       </c>
       <c r="K18" t="n">
-        <v>4.440892934799194</v>
+        <v>4.104024887084961</v>
       </c>
       <c r="L18" t="n">
-        <v>4.100507473945617</v>
+        <v>4.003968358039856</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>5.208724737167358</v>
+        <v>4.429155588150024</v>
       </c>
       <c r="C19" t="n">
-        <v>5.215865612030029</v>
+        <v>4.231683492660522</v>
       </c>
       <c r="D19" t="n">
-        <v>5.608041286468506</v>
+        <v>4.439128160476685</v>
       </c>
       <c r="E19" t="n">
-        <v>5.459707975387573</v>
+        <v>4.236670017242432</v>
       </c>
       <c r="F19" t="n">
-        <v>5.233756065368652</v>
+        <v>5.025561094284058</v>
       </c>
       <c r="G19" t="n">
-        <v>5.676536321640015</v>
+        <v>4.631613731384277</v>
       </c>
       <c r="H19" t="n">
-        <v>4.919986486434937</v>
+        <v>4.949763059616089</v>
       </c>
       <c r="I19" t="n">
-        <v>4.761539697647095</v>
+        <v>4.81213116645813</v>
       </c>
       <c r="J19" t="n">
-        <v>4.779972553253174</v>
+        <v>4.86879825592041</v>
       </c>
       <c r="K19" t="n">
-        <v>4.909279584884644</v>
+        <v>4.576760768890381</v>
       </c>
       <c r="L19" t="n">
-        <v>5.177341032028198</v>
+        <v>4.620126533508301</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>5.301139354705811</v>
+        <v>3.935476064682007</v>
       </c>
       <c r="C20" t="n">
-        <v>4.218234539031982</v>
+        <v>4.544846057891846</v>
       </c>
       <c r="D20" t="n">
-        <v>4.757652521133423</v>
+        <v>4.419182062149048</v>
       </c>
       <c r="E20" t="n">
-        <v>4.520599842071533</v>
+        <v>4.637587070465088</v>
       </c>
       <c r="F20" t="n">
-        <v>4.651398420333862</v>
+        <v>4.321442842483521</v>
       </c>
       <c r="G20" t="n">
-        <v>4.601274967193604</v>
+        <v>4.287642478942871</v>
       </c>
       <c r="H20" t="n">
-        <v>6.494558572769165</v>
+        <v>3.890596389770508</v>
       </c>
       <c r="I20" t="n">
-        <v>5.25841498374939</v>
+        <v>4.453075647354126</v>
       </c>
       <c r="J20" t="n">
-        <v>4.812744617462158</v>
+        <v>4.415192365646362</v>
       </c>
       <c r="K20" t="n">
-        <v>4.723486423492432</v>
+        <v>4.287534713745117</v>
       </c>
       <c r="L20" t="n">
-        <v>4.933950424194336</v>
+        <v>4.319257569313049</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>5.075468063354492</v>
+        <v>4.894909858703613</v>
       </c>
       <c r="C21" t="n">
-        <v>4.505183219909668</v>
+        <v>5.20806622505188</v>
       </c>
       <c r="D21" t="n">
-        <v>4.279792070388794</v>
+        <v>5.127714395523071</v>
       </c>
       <c r="E21" t="n">
-        <v>5.151172161102295</v>
+        <v>4.436240673065186</v>
       </c>
       <c r="F21" t="n">
-        <v>4.745901346206665</v>
+        <v>4.770034074783325</v>
       </c>
       <c r="G21" t="n">
-        <v>4.622566223144531</v>
+        <v>4.134769439697266</v>
       </c>
       <c r="H21" t="n">
-        <v>4.963420867919922</v>
+        <v>4.865690946578979</v>
       </c>
       <c r="I21" t="n">
-        <v>4.809293270111084</v>
+        <v>4.378075838088989</v>
       </c>
       <c r="J21" t="n">
-        <v>4.798333168029785</v>
+        <v>4.857044219970703</v>
       </c>
       <c r="K21" t="n">
-        <v>5.046721696853638</v>
+        <v>5.513830184936523</v>
       </c>
       <c r="L21" t="n">
-        <v>4.799785208702088</v>
+        <v>4.818637585639953</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>4.425394773483276</v>
+        <v>4.474914073944092</v>
       </c>
       <c r="C22" t="n">
-        <v>4.501240253448486</v>
+        <v>4.906033754348755</v>
       </c>
       <c r="D22" t="n">
-        <v>4.496384382247925</v>
+        <v>4.65714430809021</v>
       </c>
       <c r="E22" t="n">
-        <v>4.195259809494019</v>
+        <v>4.230154037475586</v>
       </c>
       <c r="F22" t="n">
-        <v>4.708981037139893</v>
+        <v>4.736852645874023</v>
       </c>
       <c r="G22" t="n">
-        <v>4.668673276901245</v>
+        <v>4.047676563262939</v>
       </c>
       <c r="H22" t="n">
-        <v>4.280372858047485</v>
+        <v>4.912307977676392</v>
       </c>
       <c r="I22" t="n">
-        <v>4.800435304641724</v>
+        <v>4.84546422958374</v>
       </c>
       <c r="J22" t="n">
-        <v>4.812238693237305</v>
+        <v>4.758274555206299</v>
       </c>
       <c r="K22" t="n">
-        <v>4.339900016784668</v>
+        <v>4.350365877151489</v>
       </c>
       <c r="L22" t="n">
-        <v>4.522888040542602</v>
+        <v>4.591918802261352</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>4.381999731063843</v>
+        <v>4.695106744766235</v>
       </c>
       <c r="C23" t="n">
-        <v>4.449393272399902</v>
+        <v>4.560803413391113</v>
       </c>
       <c r="D23" t="n">
-        <v>4.698634386062622</v>
+        <v>5.120307207107544</v>
       </c>
       <c r="E23" t="n">
-        <v>5.23745584487915</v>
+        <v>4.749298572540283</v>
       </c>
       <c r="F23" t="n">
-        <v>4.649771451950073</v>
+        <v>5.470371723175049</v>
       </c>
       <c r="G23" t="n">
-        <v>4.581165790557861</v>
+        <v>4.381282329559326</v>
       </c>
       <c r="H23" t="n">
-        <v>4.106287240982056</v>
+        <v>4.885935068130493</v>
       </c>
       <c r="I23" t="n">
-        <v>5.346244096755981</v>
+        <v>5.011428117752075</v>
       </c>
       <c r="J23" t="n">
-        <v>4.257312059402466</v>
+        <v>5.143646478652954</v>
       </c>
       <c r="K23" t="n">
-        <v>4.519843816757202</v>
+        <v>5.161556005477905</v>
       </c>
       <c r="L23" t="n">
-        <v>4.622810769081116</v>
+        <v>4.917973566055298</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>4.479394435882568</v>
+        <v>4.677161931991577</v>
       </c>
       <c r="C24" t="n">
-        <v>4.348081111907959</v>
+        <v>4.874962329864502</v>
       </c>
       <c r="D24" t="n">
-        <v>4.211849689483643</v>
+        <v>4.987662553787231</v>
       </c>
       <c r="E24" t="n">
-        <v>5.246099472045898</v>
+        <v>5.157207727432251</v>
       </c>
       <c r="F24" t="n">
-        <v>4.226119756698608</v>
+        <v>4.643583059310913</v>
       </c>
       <c r="G24" t="n">
-        <v>4.381575584411621</v>
+        <v>4.340389966964722</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5942063331604</v>
+        <v>4.282546520233154</v>
       </c>
       <c r="I24" t="n">
-        <v>4.467034578323364</v>
+        <v>4.679486274719238</v>
       </c>
       <c r="J24" t="n">
-        <v>4.293211698532104</v>
+        <v>4.345378637313843</v>
       </c>
       <c r="K24" t="n">
-        <v>4.524291276931763</v>
+        <v>4.371310472488403</v>
       </c>
       <c r="L24" t="n">
-        <v>4.477186393737793</v>
+        <v>4.635968947410584</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>4.080237150192261</v>
+        <v>3.840056896209717</v>
       </c>
       <c r="C25" t="n">
-        <v>4.109526872634888</v>
+        <v>4.278778791427612</v>
       </c>
       <c r="D25" t="n">
-        <v>3.931687116622925</v>
+        <v>4.146392345428467</v>
       </c>
       <c r="E25" t="n">
-        <v>4.464207410812378</v>
+        <v>4.258019208908081</v>
       </c>
       <c r="F25" t="n">
-        <v>3.982470512390137</v>
+        <v>3.72067666053772</v>
       </c>
       <c r="G25" t="n">
-        <v>4.354135513305664</v>
+        <v>3.774506568908691</v>
       </c>
       <c r="H25" t="n">
-        <v>4.116539478302002</v>
+        <v>3.908945798873901</v>
       </c>
       <c r="I25" t="n">
-        <v>3.871894359588623</v>
+        <v>3.790482997894287</v>
       </c>
       <c r="J25" t="n">
-        <v>4.178442478179932</v>
+        <v>3.55274772644043</v>
       </c>
       <c r="K25" t="n">
-        <v>3.716355323791504</v>
+        <v>4.133865118026733</v>
       </c>
       <c r="L25" t="n">
-        <v>4.080549621582032</v>
+        <v>3.940447211265564</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>5.207492589950562</v>
+        <v>4.520590305328369</v>
       </c>
       <c r="C26" t="n">
-        <v>4.624692440032959</v>
+        <v>4.35930871963501</v>
       </c>
       <c r="D26" t="n">
-        <v>4.900219440460205</v>
+        <v>4.399889707565308</v>
       </c>
       <c r="E26" t="n">
-        <v>5.036291360855103</v>
+        <v>4.853987216949463</v>
       </c>
       <c r="F26" t="n">
-        <v>5.02853798866272</v>
+        <v>4.591272592544556</v>
       </c>
       <c r="G26" t="n">
-        <v>5.191291332244873</v>
+        <v>4.620049238204956</v>
       </c>
       <c r="H26" t="n">
-        <v>4.584923982620239</v>
+        <v>4.351596832275391</v>
       </c>
       <c r="I26" t="n">
-        <v>4.726480960845947</v>
+        <v>4.767117500305176</v>
       </c>
       <c r="J26" t="n">
-        <v>4.798008441925049</v>
+        <v>4.352888822555542</v>
       </c>
       <c r="K26" t="n">
-        <v>4.764529943466187</v>
+        <v>4.315222024917603</v>
       </c>
       <c r="L26" t="n">
-        <v>4.886246848106384</v>
+        <v>4.513192296028137</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>4.821855545043945</v>
+        <v>5.177849054336548</v>
       </c>
       <c r="C27" t="n">
-        <v>4.843929767608643</v>
+        <v>5.585548162460327</v>
       </c>
       <c r="D27" t="n">
-        <v>5.681822061538696</v>
+        <v>4.92471981048584</v>
       </c>
       <c r="E27" t="n">
-        <v>4.880771398544312</v>
+        <v>4.905748128890991</v>
       </c>
       <c r="F27" t="n">
-        <v>5.608209848403931</v>
+        <v>5.010354518890381</v>
       </c>
       <c r="G27" t="n">
-        <v>5.100964784622192</v>
+        <v>4.493777275085449</v>
       </c>
       <c r="H27" t="n">
-        <v>5.137696266174316</v>
+        <v>5.214880466461182</v>
       </c>
       <c r="I27" t="n">
-        <v>4.962549448013306</v>
+        <v>4.889380693435669</v>
       </c>
       <c r="J27" t="n">
-        <v>5.076812744140625</v>
+        <v>4.336927652359009</v>
       </c>
       <c r="K27" t="n">
-        <v>5.066333055496216</v>
+        <v>5.030690908432007</v>
       </c>
       <c r="L27" t="n">
-        <v>5.118094491958618</v>
+        <v>4.95698766708374</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>4.521929025650024</v>
+        <v>4.212908029556274</v>
       </c>
       <c r="C28" t="n">
-        <v>4.310056686401367</v>
+        <v>4.011367559432983</v>
       </c>
       <c r="D28" t="n">
-        <v>4.6204514503479</v>
+        <v>4.386065006256104</v>
       </c>
       <c r="E28" t="n">
-        <v>4.647700548171997</v>
+        <v>4.168134927749634</v>
       </c>
       <c r="F28" t="n">
-        <v>4.661738634109497</v>
+        <v>4.082709312438965</v>
       </c>
       <c r="G28" t="n">
-        <v>4.438657760620117</v>
+        <v>4.187892436981201</v>
       </c>
       <c r="H28" t="n">
-        <v>4.536436557769775</v>
+        <v>4.192992448806763</v>
       </c>
       <c r="I28" t="n">
-        <v>4.795823812484741</v>
+        <v>4.52388334274292</v>
       </c>
       <c r="J28" t="n">
-        <v>4.625517845153809</v>
+        <v>4.082079648971558</v>
       </c>
       <c r="K28" t="n">
-        <v>4.711336851119995</v>
+        <v>4.158401489257812</v>
       </c>
       <c r="L28" t="n">
-        <v>4.586964917182923</v>
+        <v>4.200643420219421</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>4.29680347442627</v>
+        <v>4.787084817886353</v>
       </c>
       <c r="C29" t="n">
-        <v>4.65822172164917</v>
+        <v>4.191384792327881</v>
       </c>
       <c r="D29" t="n">
-        <v>4.174562692642212</v>
+        <v>4.178175687789917</v>
       </c>
       <c r="E29" t="n">
-        <v>5.417012453079224</v>
+        <v>3.980650901794434</v>
       </c>
       <c r="F29" t="n">
-        <v>4.183632612228394</v>
+        <v>4.357237815856934</v>
       </c>
       <c r="G29" t="n">
-        <v>4.420886516571045</v>
+        <v>4.268456935882568</v>
       </c>
       <c r="H29" t="n">
-        <v>4.951080560684204</v>
+        <v>4.140119791030884</v>
       </c>
       <c r="I29" t="n">
-        <v>4.787964344024658</v>
+        <v>4.584197759628296</v>
       </c>
       <c r="J29" t="n">
-        <v>4.217458486557007</v>
+        <v>4.300838947296143</v>
       </c>
       <c r="K29" t="n">
-        <v>4.846238851547241</v>
+        <v>4.493005752563477</v>
       </c>
       <c r="L29" t="n">
-        <v>4.595386171340943</v>
+        <v>4.328115320205688</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>4.936054468154907</v>
+        <v>3.984074115753174</v>
       </c>
       <c r="C30" t="n">
-        <v>4.498954772949219</v>
+        <v>4.328330993652344</v>
       </c>
       <c r="D30" t="n">
-        <v>4.580498933792114</v>
+        <v>4.143305778503418</v>
       </c>
       <c r="E30" t="n">
-        <v>4.46694278717041</v>
+        <v>3.878705739974976</v>
       </c>
       <c r="F30" t="n">
-        <v>4.824305057525635</v>
+        <v>4.100584506988525</v>
       </c>
       <c r="G30" t="n">
-        <v>4.64062237739563</v>
+        <v>4.131809234619141</v>
       </c>
       <c r="H30" t="n">
-        <v>4.536092281341553</v>
+        <v>4.059423923492432</v>
       </c>
       <c r="I30" t="n">
-        <v>4.751651763916016</v>
+        <v>4.760255813598633</v>
       </c>
       <c r="J30" t="n">
-        <v>4.871444225311279</v>
+        <v>4.663548707962036</v>
       </c>
       <c r="K30" t="n">
-        <v>4.615817070007324</v>
+        <v>4.123029232025146</v>
       </c>
       <c r="L30" t="n">
-        <v>4.672238373756409</v>
+        <v>4.217306804656983</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>4.536203622817993</v>
+        <v>4.527069807052612</v>
       </c>
       <c r="C31" t="n">
-        <v>4.19068169593811</v>
+        <v>4.05070161819458</v>
       </c>
       <c r="D31" t="n">
-        <v>4.058314800262451</v>
+        <v>4.264457702636719</v>
       </c>
       <c r="E31" t="n">
-        <v>4.377535820007324</v>
+        <v>3.85667896270752</v>
       </c>
       <c r="F31" t="n">
-        <v>4.399163007736206</v>
+        <v>4.155452489852905</v>
       </c>
       <c r="G31" t="n">
-        <v>4.344529390335083</v>
+        <v>4.34607720375061</v>
       </c>
       <c r="H31" t="n">
-        <v>4.02110767364502</v>
+        <v>4.06830358505249</v>
       </c>
       <c r="I31" t="n">
-        <v>3.985246419906616</v>
+        <v>3.911447286605835</v>
       </c>
       <c r="J31" t="n">
-        <v>4.603302955627441</v>
+        <v>3.91362190246582</v>
       </c>
       <c r="K31" t="n">
-        <v>4.304478645324707</v>
+        <v>4.522446155548096</v>
       </c>
       <c r="L31" t="n">
-        <v>4.282056403160095</v>
+        <v>4.161625671386719</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>4.686557054519653</v>
+        <v>4.055007696151733</v>
       </c>
       <c r="C32" t="n">
-        <v>4.560992479324341</v>
+        <v>4.095666408538818</v>
       </c>
       <c r="D32" t="n">
-        <v>4.576517820358276</v>
+        <v>3.831316709518433</v>
       </c>
       <c r="E32" t="n">
-        <v>4.575452089309692</v>
+        <v>3.948417186737061</v>
       </c>
       <c r="F32" t="n">
-        <v>4.694342136383057</v>
+        <v>4.274189472198486</v>
       </c>
       <c r="G32" t="n">
-        <v>4.222062349319458</v>
+        <v>3.890810012817383</v>
       </c>
       <c r="H32" t="n">
-        <v>4.206418991088867</v>
+        <v>4.560388565063477</v>
       </c>
       <c r="I32" t="n">
-        <v>4.226178407669067</v>
+        <v>4.294843912124634</v>
       </c>
       <c r="J32" t="n">
-        <v>4.074306011199951</v>
+        <v>3.774793148040771</v>
       </c>
       <c r="K32" t="n">
-        <v>4.294204235076904</v>
+        <v>5.117997646331787</v>
       </c>
       <c r="L32" t="n">
-        <v>4.411703157424927</v>
+        <v>4.184343075752258</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>4.473505258560181</v>
+        <v>4.365484714508057</v>
       </c>
       <c r="C33" t="n">
-        <v>4.580600261688232</v>
+        <v>4.307507038116455</v>
       </c>
       <c r="D33" t="n">
-        <v>4.457377433776855</v>
+        <v>4.682276248931885</v>
       </c>
       <c r="E33" t="n">
-        <v>4.58997917175293</v>
+        <v>4.408297061920166</v>
       </c>
       <c r="F33" t="n">
-        <v>4.590394496917725</v>
+        <v>4.074289083480835</v>
       </c>
       <c r="G33" t="n">
-        <v>4.586625337600708</v>
+        <v>4.483094692230225</v>
       </c>
       <c r="H33" t="n">
-        <v>4.73285436630249</v>
+        <v>4.674175024032593</v>
       </c>
       <c r="I33" t="n">
-        <v>4.752497434616089</v>
+        <v>4.531299114227295</v>
       </c>
       <c r="J33" t="n">
-        <v>4.666252851486206</v>
+        <v>4.547748565673828</v>
       </c>
       <c r="K33" t="n">
-        <v>4.597434282302856</v>
+        <v>4.67388391494751</v>
       </c>
       <c r="L33" t="n">
-        <v>4.602752089500427</v>
+        <v>4.474805545806885</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>3.941011667251587</v>
+        <v>3.633260488510132</v>
       </c>
       <c r="C34" t="n">
-        <v>3.879937887191772</v>
+        <v>3.759290933609009</v>
       </c>
       <c r="D34" t="n">
-        <v>3.686485767364502</v>
+        <v>3.731237888336182</v>
       </c>
       <c r="E34" t="n">
-        <v>4.234437465667725</v>
+        <v>3.830831050872803</v>
       </c>
       <c r="F34" t="n">
-        <v>3.848547458648682</v>
+        <v>3.692382097244263</v>
       </c>
       <c r="G34" t="n">
-        <v>3.813638925552368</v>
+        <v>3.660479307174683</v>
       </c>
       <c r="H34" t="n">
-        <v>4.097129106521606</v>
+        <v>3.61875057220459</v>
       </c>
       <c r="I34" t="n">
-        <v>4.189922094345093</v>
+        <v>3.805251121520996</v>
       </c>
       <c r="J34" t="n">
-        <v>4.145122528076172</v>
+        <v>3.618689775466919</v>
       </c>
       <c r="K34" t="n">
-        <v>4.133147478103638</v>
+        <v>3.637328147888184</v>
       </c>
       <c r="L34" t="n">
-        <v>3.996938037872314</v>
+        <v>3.698750138282776</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>5.272347688674927</v>
+        <v>4.555889844894409</v>
       </c>
       <c r="C35" t="n">
-        <v>5.240135669708252</v>
+        <v>5.427172660827637</v>
       </c>
       <c r="D35" t="n">
-        <v>5.470631837844849</v>
+        <v>4.439006328582764</v>
       </c>
       <c r="E35" t="n">
-        <v>4.89104175567627</v>
+        <v>4.996618509292603</v>
       </c>
       <c r="F35" t="n">
-        <v>5.964280843734741</v>
+        <v>4.851861476898193</v>
       </c>
       <c r="G35" t="n">
-        <v>5.19415283203125</v>
+        <v>4.886890888214111</v>
       </c>
       <c r="H35" t="n">
-        <v>5.450697898864746</v>
+        <v>4.506845712661743</v>
       </c>
       <c r="I35" t="n">
-        <v>5.519217252731323</v>
+        <v>4.682016372680664</v>
       </c>
       <c r="J35" t="n">
-        <v>5.107626438140869</v>
+        <v>4.891096353530884</v>
       </c>
       <c r="K35" t="n">
-        <v>5.047089099884033</v>
+        <v>4.745309829711914</v>
       </c>
       <c r="L35" t="n">
-        <v>5.315722131729126</v>
+        <v>4.798270797729492</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>3.900712966918945</v>
+        <v>4.380927801132202</v>
       </c>
       <c r="C36" t="n">
-        <v>3.679404258728027</v>
+        <v>3.602832555770874</v>
       </c>
       <c r="D36" t="n">
-        <v>3.706575155258179</v>
+        <v>3.402359247207642</v>
       </c>
       <c r="E36" t="n">
-        <v>3.852364540100098</v>
+        <v>3.365460872650146</v>
       </c>
       <c r="F36" t="n">
-        <v>3.771625757217407</v>
+        <v>3.307613134384155</v>
       </c>
       <c r="G36" t="n">
-        <v>3.659375905990601</v>
+        <v>3.442966461181641</v>
       </c>
       <c r="H36" t="n">
-        <v>3.847425937652588</v>
+        <v>3.419047117233276</v>
       </c>
       <c r="I36" t="n">
-        <v>3.6147301197052</v>
+        <v>3.388091325759888</v>
       </c>
       <c r="J36" t="n">
-        <v>3.614574193954468</v>
+        <v>3.317674875259399</v>
       </c>
       <c r="K36" t="n">
-        <v>3.814793348312378</v>
+        <v>3.360051870346069</v>
       </c>
       <c r="L36" t="n">
-        <v>3.746158218383789</v>
+        <v>3.498702526092529</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>4.915931701660156</v>
+        <v>4.146333694458008</v>
       </c>
       <c r="C37" t="n">
-        <v>5.453456163406372</v>
+        <v>4.634865522384644</v>
       </c>
       <c r="D37" t="n">
-        <v>4.761901617050171</v>
+        <v>4.793428421020508</v>
       </c>
       <c r="E37" t="n">
-        <v>5.080258846282959</v>
+        <v>4.2318434715271</v>
       </c>
       <c r="F37" t="n">
-        <v>4.613587856292725</v>
+        <v>4.360210418701172</v>
       </c>
       <c r="G37" t="n">
-        <v>5.117030620574951</v>
+        <v>4.400680065155029</v>
       </c>
       <c r="H37" t="n">
-        <v>5.051107168197632</v>
+        <v>4.410390615463257</v>
       </c>
       <c r="I37" t="n">
-        <v>4.834680795669556</v>
+        <v>4.134699583053589</v>
       </c>
       <c r="J37" t="n">
-        <v>4.99813985824585</v>
+        <v>4.321428060531616</v>
       </c>
       <c r="K37" t="n">
-        <v>4.955672740936279</v>
+        <v>4.669868946075439</v>
       </c>
       <c r="L37" t="n">
-        <v>4.978176736831665</v>
+        <v>4.410374879837036</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>4.724657773971558</v>
+        <v>5.537439584732056</v>
       </c>
       <c r="C38" t="n">
-        <v>4.512948989868164</v>
+        <v>4.329002857208252</v>
       </c>
       <c r="D38" t="n">
-        <v>5.141471862792969</v>
+        <v>4.24483847618103</v>
       </c>
       <c r="E38" t="n">
-        <v>4.980646371841431</v>
+        <v>4.829343795776367</v>
       </c>
       <c r="F38" t="n">
-        <v>4.783545732498169</v>
+        <v>4.23883318901062</v>
       </c>
       <c r="G38" t="n">
-        <v>4.780089616775513</v>
+        <v>4.266480207443237</v>
       </c>
       <c r="H38" t="n">
-        <v>5.239720344543457</v>
+        <v>4.577889919281006</v>
       </c>
       <c r="I38" t="n">
-        <v>4.851370811462402</v>
+        <v>4.212398767471313</v>
       </c>
       <c r="J38" t="n">
-        <v>5.098381280899048</v>
+        <v>4.268614053726196</v>
       </c>
       <c r="K38" t="n">
-        <v>4.864696979522705</v>
+        <v>4.473781108856201</v>
       </c>
       <c r="L38" t="n">
-        <v>4.897752976417541</v>
+        <v>4.497862195968628</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>4.532580614089966</v>
+        <v>3.842681646347046</v>
       </c>
       <c r="C39" t="n">
-        <v>4.132221937179565</v>
+        <v>3.888451814651489</v>
       </c>
       <c r="D39" t="n">
-        <v>4.060403108596802</v>
+        <v>3.517618417739868</v>
       </c>
       <c r="E39" t="n">
-        <v>4.037170171737671</v>
+        <v>4.309333562850952</v>
       </c>
       <c r="F39" t="n">
-        <v>4.18181586265564</v>
+        <v>3.494287967681885</v>
       </c>
       <c r="G39" t="n">
-        <v>4.407000303268433</v>
+        <v>3.917898654937744</v>
       </c>
       <c r="H39" t="n">
-        <v>3.877120494842529</v>
+        <v>3.72945761680603</v>
       </c>
       <c r="I39" t="n">
-        <v>4.269317150115967</v>
+        <v>4.087701797485352</v>
       </c>
       <c r="J39" t="n">
-        <v>4.119142293930054</v>
+        <v>3.992267370223999</v>
       </c>
       <c r="K39" t="n">
-        <v>4.427085876464844</v>
+        <v>3.847163677215576</v>
       </c>
       <c r="L39" t="n">
-        <v>4.204385781288147</v>
+        <v>3.862686252593994</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>4.516414165496826</v>
+        <v>4.333922386169434</v>
       </c>
       <c r="C40" t="n">
-        <v>4.847845792770386</v>
+        <v>4.541045427322388</v>
       </c>
       <c r="D40" t="n">
-        <v>4.729838132858276</v>
+        <v>4.452152729034424</v>
       </c>
       <c r="E40" t="n">
-        <v>4.601178646087646</v>
+        <v>4.642140626907349</v>
       </c>
       <c r="F40" t="n">
-        <v>4.796633958816528</v>
+        <v>4.121744155883789</v>
       </c>
       <c r="G40" t="n">
-        <v>4.464712858200073</v>
+        <v>4.854600667953491</v>
       </c>
       <c r="H40" t="n">
-        <v>4.671295642852783</v>
+        <v>4.701594114303589</v>
       </c>
       <c r="I40" t="n">
-        <v>4.664619445800781</v>
+        <v>4.60405969619751</v>
       </c>
       <c r="J40" t="n">
-        <v>4.504228353500366</v>
+        <v>4.835031747817993</v>
       </c>
       <c r="K40" t="n">
-        <v>4.549211025238037</v>
+        <v>4.219014406204224</v>
       </c>
       <c r="L40" t="n">
-        <v>4.634597802162171</v>
+        <v>4.530530595779419</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>4.639012813568115</v>
+        <v>4.292006731033325</v>
       </c>
       <c r="C41" t="n">
-        <v>5.22602653503418</v>
+        <v>4.268120050430298</v>
       </c>
       <c r="D41" t="n">
-        <v>4.594800233840942</v>
+        <v>4.130130767822266</v>
       </c>
       <c r="E41" t="n">
-        <v>5.179162740707397</v>
+        <v>4.453294277191162</v>
       </c>
       <c r="F41" t="n">
-        <v>4.659202337265015</v>
+        <v>6.086145877838135</v>
       </c>
       <c r="G41" t="n">
-        <v>5.54659628868103</v>
+        <v>4.374375581741333</v>
       </c>
       <c r="H41" t="n">
-        <v>5.442693710327148</v>
+        <v>4.155150175094604</v>
       </c>
       <c r="I41" t="n">
-        <v>4.840887784957886</v>
+        <v>4.043251514434814</v>
       </c>
       <c r="J41" t="n">
-        <v>4.889285802841187</v>
+        <v>4.064105987548828</v>
       </c>
       <c r="K41" t="n">
-        <v>4.769755363464355</v>
+        <v>4.218672275543213</v>
       </c>
       <c r="L41" t="n">
-        <v>4.978742361068726</v>
+        <v>4.408525323867797</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>4.561927080154419</v>
+        <v>4.07332181930542</v>
       </c>
       <c r="C42" t="n">
-        <v>4.607525587081909</v>
+        <v>4.281443119049072</v>
       </c>
       <c r="D42" t="n">
-        <v>5.05961537361145</v>
+        <v>4.329669237136841</v>
       </c>
       <c r="E42" t="n">
-        <v>5.313439846038818</v>
+        <v>4.068769693374634</v>
       </c>
       <c r="F42" t="n">
-        <v>4.928035497665405</v>
+        <v>4.178269863128662</v>
       </c>
       <c r="G42" t="n">
-        <v>4.641482830047607</v>
+        <v>4.255705595016479</v>
       </c>
       <c r="H42" t="n">
-        <v>4.609404325485229</v>
+        <v>4.100945949554443</v>
       </c>
       <c r="I42" t="n">
-        <v>4.459043264389038</v>
+        <v>4.513956308364868</v>
       </c>
       <c r="J42" t="n">
-        <v>4.650984287261963</v>
+        <v>4.020668745040894</v>
       </c>
       <c r="K42" t="n">
-        <v>4.246014833450317</v>
+        <v>3.990828990936279</v>
       </c>
       <c r="L42" t="n">
-        <v>4.707747292518616</v>
+        <v>4.181357932090759</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>4.793848276138306</v>
+        <v>4.544351577758789</v>
       </c>
       <c r="C43" t="n">
-        <v>5.358871698379517</v>
+        <v>4.266030311584473</v>
       </c>
       <c r="D43" t="n">
-        <v>4.541485786437988</v>
+        <v>4.235239505767822</v>
       </c>
       <c r="E43" t="n">
-        <v>5.017696857452393</v>
+        <v>4.307833194732666</v>
       </c>
       <c r="F43" t="n">
-        <v>4.556081533432007</v>
+        <v>4.56793999671936</v>
       </c>
       <c r="G43" t="n">
-        <v>4.987009525299072</v>
+        <v>5.165791988372803</v>
       </c>
       <c r="H43" t="n">
-        <v>4.913623571395874</v>
+        <v>4.772859334945679</v>
       </c>
       <c r="I43" t="n">
-        <v>4.38068962097168</v>
+        <v>4.782312870025635</v>
       </c>
       <c r="J43" t="n">
-        <v>5.028362035751343</v>
+        <v>4.295443773269653</v>
       </c>
       <c r="K43" t="n">
-        <v>4.842629909515381</v>
+        <v>4.868354797363281</v>
       </c>
       <c r="L43" t="n">
-        <v>4.842029881477356</v>
+        <v>4.580615735054016</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>4.642299890518188</v>
+        <v>3.894328117370605</v>
       </c>
       <c r="C44" t="n">
-        <v>4.524835348129272</v>
+        <v>4.23941445350647</v>
       </c>
       <c r="D44" t="n">
-        <v>4.606614589691162</v>
+        <v>4.224374532699585</v>
       </c>
       <c r="E44" t="n">
-        <v>4.366366624832153</v>
+        <v>4.244801998138428</v>
       </c>
       <c r="F44" t="n">
-        <v>4.570545434951782</v>
+        <v>3.994277954101562</v>
       </c>
       <c r="G44" t="n">
-        <v>4.6602783203125</v>
+        <v>4.03636646270752</v>
       </c>
       <c r="H44" t="n">
-        <v>4.145175457000732</v>
+        <v>3.991532325744629</v>
       </c>
       <c r="I44" t="n">
-        <v>4.178847789764404</v>
+        <v>4.043443202972412</v>
       </c>
       <c r="J44" t="n">
-        <v>4.17454719543457</v>
+        <v>4.406903266906738</v>
       </c>
       <c r="K44" t="n">
-        <v>4.877611875534058</v>
+        <v>4.092708349227905</v>
       </c>
       <c r="L44" t="n">
-        <v>4.474712252616882</v>
+        <v>4.116815066337585</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>4.507548332214355</v>
+        <v>3.745377063751221</v>
       </c>
       <c r="C45" t="n">
-        <v>4.124598264694214</v>
+        <v>4.244311571121216</v>
       </c>
       <c r="D45" t="n">
-        <v>4.382124185562134</v>
+        <v>3.743659019470215</v>
       </c>
       <c r="E45" t="n">
-        <v>4.40795636177063</v>
+        <v>4.13441801071167</v>
       </c>
       <c r="F45" t="n">
-        <v>4.470187664031982</v>
+        <v>4.027278184890747</v>
       </c>
       <c r="G45" t="n">
-        <v>4.389004468917847</v>
+        <v>3.935664176940918</v>
       </c>
       <c r="H45" t="n">
-        <v>4.281875848770142</v>
+        <v>3.758329391479492</v>
       </c>
       <c r="I45" t="n">
-        <v>4.652374505996704</v>
+        <v>4.020210981369019</v>
       </c>
       <c r="J45" t="n">
-        <v>4.465412855148315</v>
+        <v>3.856486558914185</v>
       </c>
       <c r="K45" t="n">
-        <v>4.493904590606689</v>
+        <v>3.977657079696655</v>
       </c>
       <c r="L45" t="n">
-        <v>4.417498707771301</v>
+        <v>3.944339203834534</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>4.357842445373535</v>
+        <v>3.741885185241699</v>
       </c>
       <c r="C46" t="n">
-        <v>4.592352390289307</v>
+        <v>3.902508735656738</v>
       </c>
       <c r="D46" t="n">
-        <v>4.759640216827393</v>
+        <v>4.039679288864136</v>
       </c>
       <c r="E46" t="n">
-        <v>4.540373086929321</v>
+        <v>3.754229307174683</v>
       </c>
       <c r="F46" t="n">
-        <v>4.112665414810181</v>
+        <v>4.170480728149414</v>
       </c>
       <c r="G46" t="n">
-        <v>4.804332971572876</v>
+        <v>3.862935304641724</v>
       </c>
       <c r="H46" t="n">
-        <v>4.185888051986694</v>
+        <v>3.965427160263062</v>
       </c>
       <c r="I46" t="n">
-        <v>4.553939580917358</v>
+        <v>4.450422048568726</v>
       </c>
       <c r="J46" t="n">
-        <v>4.66770601272583</v>
+        <v>3.84013032913208</v>
       </c>
       <c r="K46" t="n">
-        <v>4.699593782424927</v>
+        <v>3.815497636795044</v>
       </c>
       <c r="L46" t="n">
-        <v>4.527433395385742</v>
+        <v>3.954319572448731</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>4.68403172492981</v>
+        <v>4.481888771057129</v>
       </c>
       <c r="C47" t="n">
-        <v>4.628214597702026</v>
+        <v>4.031949520111084</v>
       </c>
       <c r="D47" t="n">
-        <v>5.237031936645508</v>
+        <v>4.605175495147705</v>
       </c>
       <c r="E47" t="n">
-        <v>4.881213903427124</v>
+        <v>4.551243305206299</v>
       </c>
       <c r="F47" t="n">
-        <v>4.502320051193237</v>
+        <v>4.416844129562378</v>
       </c>
       <c r="G47" t="n">
-        <v>5.605099201202393</v>
+        <v>4.093532800674438</v>
       </c>
       <c r="H47" t="n">
-        <v>4.60761022567749</v>
+        <v>4.669252872467041</v>
       </c>
       <c r="I47" t="n">
-        <v>4.229815006256104</v>
+        <v>3.856522083282471</v>
       </c>
       <c r="J47" t="n">
-        <v>5.046821594238281</v>
+        <v>4.560304880142212</v>
       </c>
       <c r="K47" t="n">
-        <v>4.651384353637695</v>
+        <v>4.882119417190552</v>
       </c>
       <c r="L47" t="n">
-        <v>4.807354259490967</v>
+        <v>4.414883327484131</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.426002740859985</v>
+        <v>3.826021432876587</v>
       </c>
       <c r="C48" t="n">
-        <v>5.568570137023926</v>
+        <v>4.248739004135132</v>
       </c>
       <c r="D48" t="n">
-        <v>4.854780912399292</v>
+        <v>4.017096519470215</v>
       </c>
       <c r="E48" t="n">
-        <v>4.971781492233276</v>
+        <v>4.20323634147644</v>
       </c>
       <c r="F48" t="n">
-        <v>4.576510190963745</v>
+        <v>4.382735013961792</v>
       </c>
       <c r="G48" t="n">
-        <v>4.775537729263306</v>
+        <v>4.08826732635498</v>
       </c>
       <c r="H48" t="n">
-        <v>4.829434156417847</v>
+        <v>4.0912926197052</v>
       </c>
       <c r="I48" t="n">
-        <v>4.737893342971802</v>
+        <v>4.336759805679321</v>
       </c>
       <c r="J48" t="n">
-        <v>5.033056497573853</v>
+        <v>4.644194602966309</v>
       </c>
       <c r="K48" t="n">
-        <v>4.635876655578613</v>
+        <v>4.049862861633301</v>
       </c>
       <c r="L48" t="n">
-        <v>4.840944385528564</v>
+        <v>4.188820552825928</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>5.04655647277832</v>
+        <v>4.400989770889282</v>
       </c>
       <c r="C49" t="n">
-        <v>4.971224308013916</v>
+        <v>4.507655143737793</v>
       </c>
       <c r="D49" t="n">
-        <v>5.360738039016724</v>
+        <v>4.537884712219238</v>
       </c>
       <c r="E49" t="n">
-        <v>4.679548501968384</v>
+        <v>4.79541015625</v>
       </c>
       <c r="F49" t="n">
-        <v>4.670042276382446</v>
+        <v>4.876491785049438</v>
       </c>
       <c r="G49" t="n">
-        <v>5.47491192817688</v>
+        <v>5.194306135177612</v>
       </c>
       <c r="H49" t="n">
-        <v>4.914647579193115</v>
+        <v>4.624937057495117</v>
       </c>
       <c r="I49" t="n">
-        <v>4.476065397262573</v>
+        <v>4.908275127410889</v>
       </c>
       <c r="J49" t="n">
-        <v>4.776948213577271</v>
+        <v>4.820735931396484</v>
       </c>
       <c r="K49" t="n">
-        <v>4.574779272079468</v>
+        <v>4.308438539505005</v>
       </c>
       <c r="L49" t="n">
-        <v>4.894546198844909</v>
+        <v>4.697512435913086</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>3.988427400588989</v>
+        <v>3.385408401489258</v>
       </c>
       <c r="C50" t="n">
-        <v>3.790073156356812</v>
+        <v>3.573229312896729</v>
       </c>
       <c r="D50" t="n">
-        <v>3.995693445205688</v>
+        <v>3.547624826431274</v>
       </c>
       <c r="E50" t="n">
-        <v>3.857639074325562</v>
+        <v>3.385932683944702</v>
       </c>
       <c r="F50" t="n">
-        <v>3.733517169952393</v>
+        <v>3.514891147613525</v>
       </c>
       <c r="G50" t="n">
-        <v>3.760093688964844</v>
+        <v>3.345080614089966</v>
       </c>
       <c r="H50" t="n">
-        <v>4.015035152435303</v>
+        <v>3.458142518997192</v>
       </c>
       <c r="I50" t="n">
-        <v>3.412541627883911</v>
+        <v>3.404244184494019</v>
       </c>
       <c r="J50" t="n">
-        <v>3.760979175567627</v>
+        <v>3.218188524246216</v>
       </c>
       <c r="K50" t="n">
-        <v>3.661065101623535</v>
+        <v>3.218872308731079</v>
       </c>
       <c r="L50" t="n">
-        <v>3.797506499290466</v>
+        <v>3.405161452293396</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>4.794213771820068</v>
+        <v>4.732003450393677</v>
       </c>
       <c r="C51" t="n">
-        <v>4.794263362884521</v>
+        <v>4.114906072616577</v>
       </c>
       <c r="D51" t="n">
-        <v>4.429585456848145</v>
+        <v>4.36588191986084</v>
       </c>
       <c r="E51" t="n">
-        <v>4.255249261856079</v>
+        <v>4.222030878067017</v>
       </c>
       <c r="F51" t="n">
-        <v>4.242883682250977</v>
+        <v>4.170435190200806</v>
       </c>
       <c r="G51" t="n">
-        <v>4.510222434997559</v>
+        <v>3.788218259811401</v>
       </c>
       <c r="H51" t="n">
-        <v>5.011589288711548</v>
+        <v>3.917745590209961</v>
       </c>
       <c r="I51" t="n">
-        <v>4.527149438858032</v>
+        <v>3.939471006393433</v>
       </c>
       <c r="J51" t="n">
-        <v>4.476590394973755</v>
+        <v>4.022556781768799</v>
       </c>
       <c r="K51" t="n">
-        <v>4.298600196838379</v>
+        <v>3.911338806152344</v>
       </c>
       <c r="L51" t="n">
-        <v>4.534034729003906</v>
+        <v>4.118458795547485</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.601727433204651</v>
+        <v>4.359997863769531</v>
       </c>
       <c r="C52" t="n">
-        <v>4.620738635063171</v>
+        <v>4.363516502380371</v>
       </c>
       <c r="D52" t="n">
-        <v>4.577550187110901</v>
+        <v>4.335764589309693</v>
       </c>
       <c r="E52" t="n">
-        <v>4.664869017601013</v>
+        <v>4.339841833114624</v>
       </c>
       <c r="F52" t="n">
-        <v>4.578164315223693</v>
+        <v>4.396554560661316</v>
       </c>
       <c r="G52" t="n">
-        <v>4.690426568984986</v>
+        <v>4.292376236915588</v>
       </c>
       <c r="H52" t="n">
-        <v>4.629588036537171</v>
+        <v>4.326245746612549</v>
       </c>
       <c r="I52" t="n">
-        <v>4.534046297073364</v>
+        <v>4.365907688140869</v>
       </c>
       <c r="J52" t="n">
-        <v>4.564331235885621</v>
+        <v>4.332084474563598</v>
       </c>
       <c r="K52" t="n">
-        <v>4.59751492023468</v>
+        <v>4.392929530143737</v>
       </c>
       <c r="L52" t="n">
-        <v>4.605895664691926</v>
+        <v>4.350521902561187</v>
       </c>
     </row>
   </sheetData>
